--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_food_wholesalers.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_food_wholesalers.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="cose_tess_n0000" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.503</v>
+        <v>-0.452</v>
       </c>
       <c r="G2">
-        <v>-3.24074074074074</v>
+        <v>1.465116279069768</v>
       </c>
       <c r="H2">
-        <v>-3.24074074074074</v>
+        <v>1.465116279069768</v>
       </c>
       <c r="I2">
-        <v>-3.037037037037037</v>
+        <v>3.511627906976744</v>
       </c>
       <c r="J2">
-        <v>-3.037037037037037</v>
+        <v>3.511627906976744</v>
       </c>
       <c r="K2">
-        <v>-0.185</v>
+        <v>0.143</v>
       </c>
       <c r="L2">
-        <v>-3.425925925925926</v>
+        <v>3.325581395348837</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +626,73 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.028</v>
+        <v>0.044</v>
       </c>
       <c r="V2">
-        <v>0.01007194244604317</v>
+        <v>0.02699386503067485</v>
       </c>
       <c r="W2">
-        <v>-0.2769461077844311</v>
+        <v>0.437308868501529</v>
       </c>
       <c r="X2">
-        <v>0.1332732509700894</v>
+        <v>0.2185029924316599</v>
       </c>
       <c r="Y2">
-        <v>-0.4102193587545205</v>
+        <v>0.2188058760698691</v>
       </c>
       <c r="Z2">
-        <v>0.02193338748984565</v>
+        <v>0.01964367291000457</v>
       </c>
       <c r="AA2">
-        <v>-0.06661251015434606</v>
+        <v>0.06898126998629511</v>
       </c>
       <c r="AB2">
-        <v>0.1124374396339238</v>
+        <v>0.2005069552591772</v>
       </c>
       <c r="AC2">
-        <v>-0.1790499497882699</v>
+        <v>-0.1315256852728821</v>
       </c>
       <c r="AD2">
-        <v>1.89</v>
+        <v>0.823</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.89</v>
+        <v>0.823</v>
       </c>
       <c r="AG2">
-        <v>1.862</v>
+        <v>0.7789999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.4047109207708779</v>
+        <v>0.3355075417855687</v>
       </c>
       <c r="AI2">
-        <v>0.8525033829499322</v>
+        <v>0.6051470588235295</v>
       </c>
       <c r="AJ2">
-        <v>0.4011202068074106</v>
+        <v>0.3233706932337069</v>
       </c>
       <c r="AK2">
-        <v>0.8506167199634536</v>
+        <v>0.5919452887537994</v>
       </c>
       <c r="AL2">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
       <c r="AM2">
-        <v>0.022</v>
-      </c>
-      <c r="AN2">
-        <v>-12.11538461538461</v>
+        <v>0.008</v>
       </c>
       <c r="AO2">
-        <v>-7.454545454545455</v>
-      </c>
-      <c r="AP2">
-        <v>-11.93589743589743</v>
+        <v>15.1</v>
       </c>
       <c r="AQ2">
-        <v>-7.454545454545455</v>
+        <v>18.875</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +712,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.503</v>
+        <v>-0.452</v>
       </c>
       <c r="G3">
-        <v>-3.24074074074074</v>
+        <v>1.465116279069768</v>
       </c>
       <c r="H3">
-        <v>-3.24074074074074</v>
+        <v>1.465116279069768</v>
       </c>
       <c r="I3">
-        <v>-3.037037037037037</v>
+        <v>3.511627906976744</v>
       </c>
       <c r="J3">
-        <v>-3.037037037037037</v>
+        <v>3.511627906976744</v>
       </c>
       <c r="K3">
-        <v>-0.185</v>
+        <v>0.143</v>
       </c>
       <c r="L3">
-        <v>-3.425925925925926</v>
+        <v>3.325581395348837</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +739,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +748,8785 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.028</v>
+        <v>0.044</v>
       </c>
       <c r="V3">
-        <v>0.01007194244604317</v>
+        <v>0.02699386503067485</v>
       </c>
       <c r="W3">
-        <v>-0.2769461077844311</v>
+        <v>0.437308868501529</v>
       </c>
       <c r="X3">
-        <v>0.1332732509700894</v>
+        <v>0.2185029924316599</v>
       </c>
       <c r="Y3">
-        <v>-0.4102193587545205</v>
+        <v>0.2188058760698691</v>
       </c>
       <c r="Z3">
-        <v>0.02193338748984565</v>
+        <v>0.01964367291000457</v>
       </c>
       <c r="AA3">
-        <v>-0.06661251015434606</v>
+        <v>0.06898126998629511</v>
       </c>
       <c r="AB3">
-        <v>0.1124374396339238</v>
+        <v>0.2005069552591772</v>
       </c>
       <c r="AC3">
-        <v>-0.1790499497882699</v>
+        <v>-0.1315256852728821</v>
       </c>
       <c r="AD3">
-        <v>1.89</v>
+        <v>0.823</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.89</v>
+        <v>0.823</v>
       </c>
       <c r="AG3">
-        <v>1.862</v>
+        <v>0.7789999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.4047109207708779</v>
+        <v>0.3355075417855687</v>
       </c>
       <c r="AI3">
-        <v>0.8525033829499322</v>
+        <v>0.6051470588235295</v>
       </c>
       <c r="AJ3">
-        <v>0.4011202068074106</v>
+        <v>0.3233706932337069</v>
       </c>
       <c r="AK3">
-        <v>0.8506167199634536</v>
+        <v>0.5919452887537994</v>
       </c>
       <c r="AL3">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
       <c r="AM3">
-        <v>0.022</v>
-      </c>
-      <c r="AN3">
-        <v>-12.11538461538461</v>
+        <v>0.008</v>
       </c>
       <c r="AO3">
-        <v>-7.454545454545455</v>
-      </c>
-      <c r="AP3">
-        <v>-11.93589743589743</v>
+        <v>15.1</v>
       </c>
       <c r="AQ3">
-        <v>-7.454545454545455</v>
+        <v>18.875</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tess Agro PLC (COSE:TESS.N0000)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COSE:TESS.N0000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Food Wholesalers</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.335507541785569</v>
+      </c>
+      <c r="F2">
+        <v>0.24</v>
+      </c>
+      <c r="G2">
+        <v>1.63</v>
+      </c>
+      <c r="H2">
+        <v>2.61958876063384</v>
+      </c>
+      <c r="I2">
+        <v>2.409</v>
+      </c>
+      <c r="J2">
+        <v>3.16430876063384</v>
+      </c>
+      <c r="K2">
+        <v>0.823</v>
+      </c>
+      <c r="L2">
+        <v>0.58872</v>
+      </c>
+      <c r="M2">
+        <v>0.200506955259177</v>
+      </c>
+      <c r="N2">
+        <v>0.161908105019855</v>
+      </c>
+      <c r="O2">
+        <v>0.164864743119266</v>
+      </c>
+      <c r="P2">
+        <v>0.0418</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.21850299243166</v>
+      </c>
+      <c r="T2">
+        <v>0.199836980289283</v>
+      </c>
+      <c r="U2">
+        <v>0.674913958838913</v>
+      </c>
+      <c r="V2">
+        <v>0.604809660739714</v>
+      </c>
+      <c r="W2">
+        <v>4.663430060902544</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>1.63</v>
+      </c>
+      <c r="AB2">
+        <v>0.2662605952628563</v>
+      </c>
+      <c r="AC2">
+        <v>0.2169272935779817</v>
+      </c>
+      <c r="AD2">
+        <v>0.24</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>-0.151</v>
+      </c>
+      <c r="AI2">
+        <v>-0.134</v>
+      </c>
+      <c r="AJ2">
+        <v>0.823</v>
+      </c>
+      <c r="AK2">
+        <v>0.823</v>
+      </c>
+      <c r="AL2">
+        <v>0.01</v>
+      </c>
+      <c r="AM2">
+        <v>0.8230000000000001</v>
+      </c>
+      <c r="AN2">
+        <v>0.044</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1686685324913569</v>
+      </c>
+      <c r="C2">
+        <v>3.043587719567737</v>
+      </c>
+      <c r="D2">
+        <v>2.999587719567737</v>
+      </c>
+      <c r="E2">
+        <v>-0.823</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.044</v>
+      </c>
+      <c r="H2">
+        <v>1.63</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>-0.151</v>
+      </c>
+      <c r="L2">
+        <v>0.151</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.151</v>
+      </c>
+      <c r="O2">
+        <v>0.03623999999999999</v>
+      </c>
+      <c r="P2">
+        <v>0.11476</v>
+      </c>
+      <c r="Q2">
+        <v>-0.03623999999999999</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1686685324913569</v>
+      </c>
+      <c r="T2">
+        <v>0.4877497264029954</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.24</v>
+      </c>
+      <c r="W2">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1683161680133776</v>
+      </c>
+      <c r="C3">
+        <v>3.027218462563541</v>
+      </c>
+      <c r="D3">
+        <v>3.007748462563541</v>
+      </c>
+      <c r="E3">
+        <v>-0.7984699999999999</v>
+      </c>
+      <c r="F3">
+        <v>0.02453</v>
+      </c>
+      <c r="G3">
+        <v>0.044</v>
+      </c>
+      <c r="H3">
+        <v>1.63</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>-0.151</v>
+      </c>
+      <c r="L3">
+        <v>0.151</v>
+      </c>
+      <c r="M3">
+        <v>0.001121021</v>
+      </c>
+      <c r="N3">
+        <v>0.149878979</v>
+      </c>
+      <c r="O3">
+        <v>0.03597095496</v>
+      </c>
+      <c r="P3">
+        <v>0.11390802404</v>
+      </c>
+      <c r="Q3">
+        <v>-0.03709197596</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1696655030438158</v>
+      </c>
+      <c r="T3">
+        <v>0.4914940677369982</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.24</v>
+      </c>
+      <c r="W3">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>134.6986363324148</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1679638035353984</v>
+      </c>
+      <c r="C4">
+        <v>3.010893731283532</v>
+      </c>
+      <c r="D4">
+        <v>3.015953731283532</v>
+      </c>
+      <c r="E4">
+        <v>-0.77394</v>
+      </c>
+      <c r="F4">
+        <v>0.04906</v>
+      </c>
+      <c r="G4">
+        <v>0.044</v>
+      </c>
+      <c r="H4">
+        <v>1.63</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>-0.151</v>
+      </c>
+      <c r="L4">
+        <v>0.151</v>
+      </c>
+      <c r="M4">
+        <v>0.002242042</v>
+      </c>
+      <c r="N4">
+        <v>0.148757958</v>
+      </c>
+      <c r="O4">
+        <v>0.03570190992</v>
+      </c>
+      <c r="P4">
+        <v>0.11305604808</v>
+      </c>
+      <c r="Q4">
+        <v>-0.03794395192</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.17068281993408</v>
+      </c>
+      <c r="T4">
+        <v>0.4953148242002663</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.24</v>
+      </c>
+      <c r="W4">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>67.34931816620741</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1676114390574191</v>
+      </c>
+      <c r="C5">
+        <v>2.994613891128883</v>
+      </c>
+      <c r="D5">
+        <v>3.024203891128883</v>
+      </c>
+      <c r="E5">
+        <v>-0.7494099999999999</v>
+      </c>
+      <c r="F5">
+        <v>0.07358999999999999</v>
+      </c>
+      <c r="G5">
+        <v>0.044</v>
+      </c>
+      <c r="H5">
+        <v>1.63</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>-0.151</v>
+      </c>
+      <c r="L5">
+        <v>0.151</v>
+      </c>
+      <c r="M5">
+        <v>0.003363063</v>
+      </c>
+      <c r="N5">
+        <v>0.147636937</v>
+      </c>
+      <c r="O5">
+        <v>0.03543286488</v>
+      </c>
+      <c r="P5">
+        <v>0.11220407212</v>
+      </c>
+      <c r="Q5">
+        <v>-0.03879592788</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.171721112430329</v>
+      </c>
+      <c r="T5">
+        <v>0.4992143591473133</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.24</v>
+      </c>
+      <c r="W5">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>44.89954544413828</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1672590745794398</v>
+      </c>
+      <c r="C6">
+        <v>2.978379311509959</v>
+      </c>
+      <c r="D6">
+        <v>3.032499311509959</v>
+      </c>
+      <c r="E6">
+        <v>-0.72488</v>
+      </c>
+      <c r="F6">
+        <v>0.09812</v>
+      </c>
+      <c r="G6">
+        <v>0.044</v>
+      </c>
+      <c r="H6">
+        <v>1.63</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>-0.151</v>
+      </c>
+      <c r="L6">
+        <v>0.151</v>
+      </c>
+      <c r="M6">
+        <v>0.004484084</v>
+      </c>
+      <c r="N6">
+        <v>0.146515916</v>
+      </c>
+      <c r="O6">
+        <v>0.03516381984</v>
+      </c>
+      <c r="P6">
+        <v>0.11135209616</v>
+      </c>
+      <c r="Q6">
+        <v>-0.03964790384</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1727810360202498</v>
+      </c>
+      <c r="T6">
+        <v>0.5031951344057569</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.24</v>
+      </c>
+      <c r="W6">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>33.67465908310371</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1669067101014606</v>
+      </c>
+      <c r="C7">
+        <v>2.962190365901461</v>
+      </c>
+      <c r="D7">
+        <v>3.040840365901461</v>
+      </c>
+      <c r="E7">
+        <v>-0.7003499999999999</v>
+      </c>
+      <c r="F7">
+        <v>0.12265</v>
+      </c>
+      <c r="G7">
+        <v>0.044</v>
+      </c>
+      <c r="H7">
+        <v>1.63</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>-0.151</v>
+      </c>
+      <c r="L7">
+        <v>0.151</v>
+      </c>
+      <c r="M7">
+        <v>0.005605105</v>
+      </c>
+      <c r="N7">
+        <v>0.145394895</v>
+      </c>
+      <c r="O7">
+        <v>0.0348947748</v>
+      </c>
+      <c r="P7">
+        <v>0.1105001202</v>
+      </c>
+      <c r="Q7">
+        <v>-0.0404998798</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1738632737910111</v>
+      </c>
+      <c r="T7">
+        <v>0.5072597154591152</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.24</v>
+      </c>
+      <c r="W7">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>26.93972726648297</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1665543456234813</v>
+      </c>
+      <c r="C8">
+        <v>2.946047431898471</v>
+      </c>
+      <c r="D8">
+        <v>3.049227431898471</v>
+      </c>
+      <c r="E8">
+        <v>-0.67582</v>
+      </c>
+      <c r="F8">
+        <v>0.14718</v>
+      </c>
+      <c r="G8">
+        <v>0.044</v>
+      </c>
+      <c r="H8">
+        <v>1.63</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>-0.151</v>
+      </c>
+      <c r="L8">
+        <v>0.151</v>
+      </c>
+      <c r="M8">
+        <v>0.006726126</v>
+      </c>
+      <c r="N8">
+        <v>0.144273874</v>
+      </c>
+      <c r="O8">
+        <v>0.03462572975999999</v>
+      </c>
+      <c r="P8">
+        <v>0.10964814424</v>
+      </c>
+      <c r="Q8">
+        <v>-0.04135185576</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1749685378973206</v>
+      </c>
+      <c r="T8">
+        <v>0.5114107769604174</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.24</v>
+      </c>
+      <c r="W8">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>22.44977272206914</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1662019811455021</v>
+      </c>
+      <c r="C9">
+        <v>2.92995089127344</v>
+      </c>
+      <c r="D9">
+        <v>3.05766089127344</v>
+      </c>
+      <c r="E9">
+        <v>-0.6512899999999999</v>
+      </c>
+      <c r="F9">
+        <v>0.17171</v>
+      </c>
+      <c r="G9">
+        <v>0.044</v>
+      </c>
+      <c r="H9">
+        <v>1.63</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>-0.151</v>
+      </c>
+      <c r="L9">
+        <v>0.151</v>
+      </c>
+      <c r="M9">
+        <v>0.007847147</v>
+      </c>
+      <c r="N9">
+        <v>0.143152853</v>
+      </c>
+      <c r="O9">
+        <v>0.03435668472</v>
+      </c>
+      <c r="P9">
+        <v>0.10879616828</v>
+      </c>
+      <c r="Q9">
+        <v>-0.04220383172</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1760975711241958</v>
+      </c>
+      <c r="T9">
+        <v>0.5156511086015323</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.24</v>
+      </c>
+      <c r="W9">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>19.24266233320212</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1658496166675228</v>
+      </c>
+      <c r="C10">
+        <v>2.9139011300341</v>
+      </c>
+      <c r="D10">
+        <v>3.0661411300341</v>
+      </c>
+      <c r="E10">
+        <v>-0.62676</v>
+      </c>
+      <c r="F10">
+        <v>0.19624</v>
+      </c>
+      <c r="G10">
+        <v>0.044</v>
+      </c>
+      <c r="H10">
+        <v>1.63</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>-0.151</v>
+      </c>
+      <c r="L10">
+        <v>0.151</v>
+      </c>
+      <c r="M10">
+        <v>0.008968168</v>
+      </c>
+      <c r="N10">
+        <v>0.142031832</v>
+      </c>
+      <c r="O10">
+        <v>0.03408763968</v>
+      </c>
+      <c r="P10">
+        <v>0.10794419232</v>
+      </c>
+      <c r="Q10">
+        <v>-0.04305580768</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1772511485516552</v>
+      </c>
+      <c r="T10">
+        <v>0.5199836213652803</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.24</v>
+      </c>
+      <c r="W10">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>16.83732954155185</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1654972521895436</v>
+      </c>
+      <c r="C11">
+        <v>2.897898538482383</v>
+      </c>
+      <c r="D11">
+        <v>3.074668538482383</v>
+      </c>
+      <c r="E11">
+        <v>-0.60223</v>
+      </c>
+      <c r="F11">
+        <v>0.22077</v>
+      </c>
+      <c r="G11">
+        <v>0.044</v>
+      </c>
+      <c r="H11">
+        <v>1.63</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>-0.151</v>
+      </c>
+      <c r="L11">
+        <v>0.151</v>
+      </c>
+      <c r="M11">
+        <v>0.010089189</v>
+      </c>
+      <c r="N11">
+        <v>0.140910811</v>
+      </c>
+      <c r="O11">
+        <v>0.03381859464</v>
+      </c>
+      <c r="P11">
+        <v>0.10709221636</v>
+      </c>
+      <c r="Q11">
+        <v>-0.04390778364</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1784300793291687</v>
+      </c>
+      <c r="T11">
+        <v>0.5244113541897699</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.24</v>
+      </c>
+      <c r="W11">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>14.96651514804609</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1651448877115644</v>
+      </c>
+      <c r="C12">
+        <v>2.881943511274276</v>
+      </c>
+      <c r="D12">
+        <v>3.083243511274276</v>
+      </c>
+      <c r="E12">
+        <v>-0.5777</v>
+      </c>
+      <c r="F12">
+        <v>0.2453</v>
+      </c>
+      <c r="G12">
+        <v>0.044</v>
+      </c>
+      <c r="H12">
+        <v>1.63</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>-0.151</v>
+      </c>
+      <c r="L12">
+        <v>0.151</v>
+      </c>
+      <c r="M12">
+        <v>0.01121021</v>
+      </c>
+      <c r="N12">
+        <v>0.13978979</v>
+      </c>
+      <c r="O12">
+        <v>0.0335495496</v>
+      </c>
+      <c r="P12">
+        <v>0.1062402404</v>
+      </c>
+      <c r="Q12">
+        <v>-0.0447597596</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1796352085684048</v>
+      </c>
+      <c r="T12">
+        <v>0.5289374810770262</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.24</v>
+      </c>
+      <c r="W12">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>13.46986363324148</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1649262832335851</v>
+      </c>
+      <c r="C13">
+        <v>2.862757447692483</v>
+      </c>
+      <c r="D13">
+        <v>3.088587447692483</v>
+      </c>
+      <c r="E13">
+        <v>-0.5531699999999999</v>
+      </c>
+      <c r="F13">
+        <v>0.26983</v>
+      </c>
+      <c r="G13">
+        <v>0.044</v>
+      </c>
+      <c r="H13">
+        <v>1.63</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>-0.151</v>
+      </c>
+      <c r="L13">
+        <v>0.151</v>
+      </c>
+      <c r="M13">
+        <v>0.012762959</v>
+      </c>
+      <c r="N13">
+        <v>0.138237041</v>
+      </c>
+      <c r="O13">
+        <v>0.03317688984</v>
+      </c>
+      <c r="P13">
+        <v>0.10506015116</v>
+      </c>
+      <c r="Q13">
+        <v>-0.04593984883999999</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1808674193635787</v>
+      </c>
+      <c r="T13">
+        <v>0.5335653186808499</v>
+      </c>
+      <c r="U13">
+        <v>0.0473</v>
+      </c>
+      <c r="V13">
+        <v>0.24</v>
+      </c>
+      <c r="W13">
+        <v>0.035948</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>11.83111220524958</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1645860787556058</v>
+      </c>
+      <c r="C14">
+        <v>2.846580926000501</v>
+      </c>
+      <c r="D14">
+        <v>3.096940926000502</v>
+      </c>
+      <c r="E14">
+        <v>-0.52864</v>
+      </c>
+      <c r="F14">
+        <v>0.29436</v>
+      </c>
+      <c r="G14">
+        <v>0.044</v>
+      </c>
+      <c r="H14">
+        <v>1.63</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>-0.151</v>
+      </c>
+      <c r="L14">
+        <v>0.151</v>
+      </c>
+      <c r="M14">
+        <v>0.013923228</v>
+      </c>
+      <c r="N14">
+        <v>0.137076772</v>
+      </c>
+      <c r="O14">
+        <v>0.03289842528</v>
+      </c>
+      <c r="P14">
+        <v>0.10417834672</v>
+      </c>
+      <c r="Q14">
+        <v>-0.04682165328000001</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.182127634949552</v>
+      </c>
+      <c r="T14">
+        <v>0.538298334412033</v>
+      </c>
+      <c r="U14">
+        <v>0.0473</v>
+      </c>
+      <c r="V14">
+        <v>0.24</v>
+      </c>
+      <c r="W14">
+        <v>0.035948</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>10.84518618814545</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1646213142776265</v>
+      </c>
+      <c r="C15">
+        <v>2.821183645835598</v>
+      </c>
+      <c r="D15">
+        <v>3.096073645835598</v>
+      </c>
+      <c r="E15">
+        <v>-0.5041099999999999</v>
+      </c>
+      <c r="F15">
+        <v>0.31889</v>
+      </c>
+      <c r="G15">
+        <v>0.044</v>
+      </c>
+      <c r="H15">
+        <v>1.63</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>-0.151</v>
+      </c>
+      <c r="L15">
+        <v>0.151</v>
+      </c>
+      <c r="M15">
+        <v>0.016295279</v>
+      </c>
+      <c r="N15">
+        <v>0.134704721</v>
+      </c>
+      <c r="O15">
+        <v>0.03232913304</v>
+      </c>
+      <c r="P15">
+        <v>0.10237558796</v>
+      </c>
+      <c r="Q15">
+        <v>-0.04862441204</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1834168210087661</v>
+      </c>
+      <c r="T15">
+        <v>0.543140155102554</v>
+      </c>
+      <c r="U15">
+        <v>0.0511</v>
+      </c>
+      <c r="V15">
+        <v>0.24</v>
+      </c>
+      <c r="W15">
+        <v>0.038836</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>9.266487551394487</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1643099897996473</v>
+      </c>
+      <c r="C16">
+        <v>2.804333381234459</v>
+      </c>
+      <c r="D16">
+        <v>3.103753381234459</v>
+      </c>
+      <c r="E16">
+        <v>-0.47958</v>
+      </c>
+      <c r="F16">
+        <v>0.34342</v>
+      </c>
+      <c r="G16">
+        <v>0.044</v>
+      </c>
+      <c r="H16">
+        <v>1.63</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>-0.151</v>
+      </c>
+      <c r="L16">
+        <v>0.151</v>
+      </c>
+      <c r="M16">
+        <v>0.017548762</v>
+      </c>
+      <c r="N16">
+        <v>0.133451238</v>
+      </c>
+      <c r="O16">
+        <v>0.03202829712</v>
+      </c>
+      <c r="P16">
+        <v>0.10142294088</v>
+      </c>
+      <c r="Q16">
+        <v>-0.04957705911999999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1847359881391248</v>
+      </c>
+      <c r="T16">
+        <v>0.5480945762742497</v>
+      </c>
+      <c r="U16">
+        <v>0.0511</v>
+      </c>
+      <c r="V16">
+        <v>0.24</v>
+      </c>
+      <c r="W16">
+        <v>0.038836</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>8.604595583437739</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.163998665321668</v>
+      </c>
+      <c r="C17">
+        <v>2.787521310165303</v>
+      </c>
+      <c r="D17">
+        <v>3.111471310165303</v>
+      </c>
+      <c r="E17">
+        <v>-0.45505</v>
+      </c>
+      <c r="F17">
+        <v>0.3679499999999999</v>
+      </c>
+      <c r="G17">
+        <v>0.044</v>
+      </c>
+      <c r="H17">
+        <v>1.63</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>-0.151</v>
+      </c>
+      <c r="L17">
+        <v>0.151</v>
+      </c>
+      <c r="M17">
+        <v>0.018802245</v>
+      </c>
+      <c r="N17">
+        <v>0.132197755</v>
+      </c>
+      <c r="O17">
+        <v>0.0317274612</v>
+      </c>
+      <c r="P17">
+        <v>0.1004702938</v>
+      </c>
+      <c r="Q17">
+        <v>-0.0505297062</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.18608619449608</v>
+      </c>
+      <c r="T17">
+        <v>0.5531655720617501</v>
+      </c>
+      <c r="U17">
+        <v>0.0511</v>
+      </c>
+      <c r="V17">
+        <v>0.24</v>
+      </c>
+      <c r="W17">
+        <v>0.038836</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>8.030955877875222</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1639183808436888</v>
+      </c>
+      <c r="C18">
+        <v>2.764987842155245</v>
+      </c>
+      <c r="D18">
+        <v>3.113467842155245</v>
+      </c>
+      <c r="E18">
+        <v>-0.43052</v>
+      </c>
+      <c r="F18">
+        <v>0.39248</v>
+      </c>
+      <c r="G18">
+        <v>0.044</v>
+      </c>
+      <c r="H18">
+        <v>1.63</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>-0.151</v>
+      </c>
+      <c r="L18">
+        <v>0.151</v>
+      </c>
+      <c r="M18">
+        <v>0.02080144</v>
+      </c>
+      <c r="N18">
+        <v>0.13019856</v>
+      </c>
+      <c r="O18">
+        <v>0.0312476544</v>
+      </c>
+      <c r="P18">
+        <v>0.0989509056</v>
+      </c>
+      <c r="Q18">
+        <v>-0.0520490944</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.187468548623439</v>
+      </c>
+      <c r="T18">
+        <v>0.558357305844191</v>
+      </c>
+      <c r="U18">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V18">
+        <v>0.24</v>
+      </c>
+      <c r="W18">
+        <v>0.04028</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>7.259112830650185</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1636214963657095</v>
+      </c>
+      <c r="C19">
+        <v>2.747863139335109</v>
+      </c>
+      <c r="D19">
+        <v>3.120873139335109</v>
+      </c>
+      <c r="E19">
+        <v>-0.40599</v>
+      </c>
+      <c r="F19">
+        <v>0.41701</v>
+      </c>
+      <c r="G19">
+        <v>0.044</v>
+      </c>
+      <c r="H19">
+        <v>1.63</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>-0.151</v>
+      </c>
+      <c r="L19">
+        <v>0.151</v>
+      </c>
+      <c r="M19">
+        <v>0.02210153</v>
+      </c>
+      <c r="N19">
+        <v>0.12889847</v>
+      </c>
+      <c r="O19">
+        <v>0.03093563279999999</v>
+      </c>
+      <c r="P19">
+        <v>0.09796283719999999</v>
+      </c>
+      <c r="Q19">
+        <v>-0.05303716280000001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1888842124888067</v>
+      </c>
+      <c r="T19">
+        <v>0.5636741416454858</v>
+      </c>
+      <c r="U19">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V19">
+        <v>0.24</v>
+      </c>
+      <c r="W19">
+        <v>0.04028</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>6.832106193553115</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1633246118877303</v>
+      </c>
+      <c r="C20">
+        <v>2.730773747089393</v>
+      </c>
+      <c r="D20">
+        <v>3.128313747089392</v>
+      </c>
+      <c r="E20">
+        <v>-0.38146</v>
+      </c>
+      <c r="F20">
+        <v>0.4415399999999999</v>
+      </c>
+      <c r="G20">
+        <v>0.044</v>
+      </c>
+      <c r="H20">
+        <v>1.63</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>-0.151</v>
+      </c>
+      <c r="L20">
+        <v>0.151</v>
+      </c>
+      <c r="M20">
+        <v>0.02340162</v>
+      </c>
+      <c r="N20">
+        <v>0.12759838</v>
+      </c>
+      <c r="O20">
+        <v>0.0306236112</v>
+      </c>
+      <c r="P20">
+        <v>0.09697476880000001</v>
+      </c>
+      <c r="Q20">
+        <v>-0.05402523119999998</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1903344047411344</v>
+      </c>
+      <c r="T20">
+        <v>0.5691206563687634</v>
+      </c>
+      <c r="U20">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V20">
+        <v>0.24</v>
+      </c>
+      <c r="W20">
+        <v>0.04028</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>6.452544738355722</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.163316527409751</v>
+      </c>
+      <c r="C21">
+        <v>2.706446858950337</v>
+      </c>
+      <c r="D21">
+        <v>3.128516858950337</v>
+      </c>
+      <c r="E21">
+        <v>-0.35693</v>
+      </c>
+      <c r="F21">
+        <v>0.46607</v>
+      </c>
+      <c r="G21">
+        <v>0.044</v>
+      </c>
+      <c r="H21">
+        <v>1.63</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>-0.151</v>
+      </c>
+      <c r="L21">
+        <v>0.151</v>
+      </c>
+      <c r="M21">
+        <v>0.02563385</v>
+      </c>
+      <c r="N21">
+        <v>0.12536615</v>
+      </c>
+      <c r="O21">
+        <v>0.030087876</v>
+      </c>
+      <c r="P21">
+        <v>0.09527827400000001</v>
+      </c>
+      <c r="Q21">
+        <v>-0.05572172599999999</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1918204042095691</v>
+      </c>
+      <c r="T21">
+        <v>0.5747016529370602</v>
+      </c>
+      <c r="U21">
+        <v>0.055</v>
+      </c>
+      <c r="V21">
+        <v>0.24</v>
+      </c>
+      <c r="W21">
+        <v>0.0418</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>5.890648497982161</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1630348429317718</v>
+      </c>
+      <c r="C22">
+        <v>2.689010316932544</v>
+      </c>
+      <c r="D22">
+        <v>3.135610316932544</v>
+      </c>
+      <c r="E22">
+        <v>-0.3324</v>
+      </c>
+      <c r="F22">
+        <v>0.4906</v>
+      </c>
+      <c r="G22">
+        <v>0.044</v>
+      </c>
+      <c r="H22">
+        <v>1.63</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>-0.151</v>
+      </c>
+      <c r="L22">
+        <v>0.151</v>
+      </c>
+      <c r="M22">
+        <v>0.026983</v>
+      </c>
+      <c r="N22">
+        <v>0.124017</v>
+      </c>
+      <c r="O22">
+        <v>0.02976407999999999</v>
+      </c>
+      <c r="P22">
+        <v>0.09425291999999999</v>
+      </c>
+      <c r="Q22">
+        <v>-0.05674708000000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1933435536647147</v>
+      </c>
+      <c r="T22">
+        <v>0.5804221744195646</v>
+      </c>
+      <c r="U22">
+        <v>0.055</v>
+      </c>
+      <c r="V22">
+        <v>0.24</v>
+      </c>
+      <c r="W22">
+        <v>0.0418</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>5.596116073083052</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1627531584537925</v>
+      </c>
+      <c r="C23">
+        <v>2.671606014787197</v>
+      </c>
+      <c r="D23">
+        <v>3.142736014787197</v>
+      </c>
+      <c r="E23">
+        <v>-0.30787</v>
+      </c>
+      <c r="F23">
+        <v>0.51513</v>
+      </c>
+      <c r="G23">
+        <v>0.044</v>
+      </c>
+      <c r="H23">
+        <v>1.63</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>-0.151</v>
+      </c>
+      <c r="L23">
+        <v>0.151</v>
+      </c>
+      <c r="M23">
+        <v>0.02833215</v>
+      </c>
+      <c r="N23">
+        <v>0.12266785</v>
+      </c>
+      <c r="O23">
+        <v>0.029440284</v>
+      </c>
+      <c r="P23">
+        <v>0.093227566</v>
+      </c>
+      <c r="Q23">
+        <v>-0.057772434</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1949052638655601</v>
+      </c>
+      <c r="T23">
+        <v>0.5862875192307399</v>
+      </c>
+      <c r="U23">
+        <v>0.055</v>
+      </c>
+      <c r="V23">
+        <v>0.24</v>
+      </c>
+      <c r="W23">
+        <v>0.0418</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>5.329634355317192</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1624714739758132</v>
+      </c>
+      <c r="C24">
+        <v>2.654234172810971</v>
+      </c>
+      <c r="D24">
+        <v>3.149894172810971</v>
+      </c>
+      <c r="E24">
+        <v>-0.28334</v>
+      </c>
+      <c r="F24">
+        <v>0.5396599999999999</v>
+      </c>
+      <c r="G24">
+        <v>0.044</v>
+      </c>
+      <c r="H24">
+        <v>1.63</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>-0.151</v>
+      </c>
+      <c r="L24">
+        <v>0.151</v>
+      </c>
+      <c r="M24">
+        <v>0.0296813</v>
+      </c>
+      <c r="N24">
+        <v>0.1213187</v>
+      </c>
+      <c r="O24">
+        <v>0.029116488</v>
+      </c>
+      <c r="P24">
+        <v>0.09220221200000001</v>
+      </c>
+      <c r="Q24">
+        <v>-0.05879778799999999</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1965070179177093</v>
+      </c>
+      <c r="T24">
+        <v>0.5923032574986119</v>
+      </c>
+      <c r="U24">
+        <v>0.055</v>
+      </c>
+      <c r="V24">
+        <v>0.24</v>
+      </c>
+      <c r="W24">
+        <v>0.0418</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.087378248257321</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.162189789497834</v>
+      </c>
+      <c r="C25">
+        <v>2.636895013312191</v>
+      </c>
+      <c r="D25">
+        <v>3.157085013312191</v>
+      </c>
+      <c r="E25">
+        <v>-0.25881</v>
+      </c>
+      <c r="F25">
+        <v>0.56419</v>
+      </c>
+      <c r="G25">
+        <v>0.044</v>
+      </c>
+      <c r="H25">
+        <v>1.63</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>-0.151</v>
+      </c>
+      <c r="L25">
+        <v>0.151</v>
+      </c>
+      <c r="M25">
+        <v>0.03103045</v>
+      </c>
+      <c r="N25">
+        <v>0.11996955</v>
+      </c>
+      <c r="O25">
+        <v>0.028792692</v>
+      </c>
+      <c r="P25">
+        <v>0.091176858</v>
+      </c>
+      <c r="Q25">
+        <v>-0.059823142</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.198150375971213</v>
+      </c>
+      <c r="T25">
+        <v>0.5984752487085067</v>
+      </c>
+      <c r="U25">
+        <v>0.055</v>
+      </c>
+      <c r="V25">
+        <v>0.24</v>
+      </c>
+      <c r="W25">
+        <v>0.0418</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>4.866187889637438</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1619081050198548</v>
+      </c>
+      <c r="C26">
+        <v>2.619588760633845</v>
+      </c>
+      <c r="D26">
+        <v>3.164308760633844</v>
+      </c>
+      <c r="E26">
+        <v>-0.23428</v>
+      </c>
+      <c r="F26">
+        <v>0.5887199999999999</v>
+      </c>
+      <c r="G26">
+        <v>0.044</v>
+      </c>
+      <c r="H26">
+        <v>1.63</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>-0.151</v>
+      </c>
+      <c r="L26">
+        <v>0.151</v>
+      </c>
+      <c r="M26">
+        <v>0.03237959999999999</v>
+      </c>
+      <c r="N26">
+        <v>0.1186204</v>
+      </c>
+      <c r="O26">
+        <v>0.028468896</v>
+      </c>
+      <c r="P26">
+        <v>0.09015150399999999</v>
+      </c>
+      <c r="Q26">
+        <v>-0.060848496</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1998369802892825</v>
+      </c>
+      <c r="T26">
+        <v>0.6048096607397143</v>
+      </c>
+      <c r="U26">
+        <v>0.055</v>
+      </c>
+      <c r="V26">
+        <v>0.24</v>
+      </c>
+      <c r="W26">
+        <v>0.0418</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>4.663430060902544</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1623484205418755</v>
+      </c>
+      <c r="C27">
+        <v>2.583781447191371</v>
+      </c>
+      <c r="D27">
+        <v>3.153031447191371</v>
+      </c>
+      <c r="E27">
+        <v>-0.20975</v>
+      </c>
+      <c r="F27">
+        <v>0.61325</v>
+      </c>
+      <c r="G27">
+        <v>0.044</v>
+      </c>
+      <c r="H27">
+        <v>1.63</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>-0.151</v>
+      </c>
+      <c r="L27">
+        <v>0.151</v>
+      </c>
+      <c r="M27">
+        <v>0.0360591</v>
+      </c>
+      <c r="N27">
+        <v>0.1149409</v>
+      </c>
+      <c r="O27">
+        <v>0.027585816</v>
+      </c>
+      <c r="P27">
+        <v>0.08735508399999999</v>
+      </c>
+      <c r="Q27">
+        <v>-0.06364491600000001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2015685607225006</v>
+      </c>
+      <c r="T27">
+        <v>0.6113129904250876</v>
+      </c>
+      <c r="U27">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V27">
+        <v>0.24</v>
+      </c>
+      <c r="W27">
+        <v>0.04468800000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>4.187569850606365</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1620956160638962</v>
+      </c>
+      <c r="C28">
+        <v>2.565716401051907</v>
+      </c>
+      <c r="D28">
+        <v>3.159496401051908</v>
+      </c>
+      <c r="E28">
+        <v>-0.1852199999999999</v>
+      </c>
+      <c r="F28">
+        <v>0.63778</v>
+      </c>
+      <c r="G28">
+        <v>0.044</v>
+      </c>
+      <c r="H28">
+        <v>1.63</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>-0.151</v>
+      </c>
+      <c r="L28">
+        <v>0.151</v>
+      </c>
+      <c r="M28">
+        <v>0.03750146400000001</v>
+      </c>
+      <c r="N28">
+        <v>0.113498536</v>
+      </c>
+      <c r="O28">
+        <v>0.02723964864</v>
+      </c>
+      <c r="P28">
+        <v>0.08625888735999998</v>
+      </c>
+      <c r="Q28">
+        <v>-0.06474111264000001</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2033469406268868</v>
+      </c>
+      <c r="T28">
+        <v>0.6179920857776331</v>
+      </c>
+      <c r="U28">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.24</v>
+      </c>
+      <c r="W28">
+        <v>0.04468800000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.026509471736889</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.162704651585917</v>
+      </c>
+      <c r="C29">
+        <v>2.525656350199837</v>
+      </c>
+      <c r="D29">
+        <v>3.143966350199837</v>
+      </c>
+      <c r="E29">
+        <v>-0.16069</v>
+      </c>
+      <c r="F29">
+        <v>0.66231</v>
+      </c>
+      <c r="G29">
+        <v>0.044</v>
+      </c>
+      <c r="H29">
+        <v>1.63</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>-0.151</v>
+      </c>
+      <c r="L29">
+        <v>0.151</v>
+      </c>
+      <c r="M29">
+        <v>0.04172553</v>
+      </c>
+      <c r="N29">
+        <v>0.10927447</v>
+      </c>
+      <c r="O29">
+        <v>0.0262258728</v>
+      </c>
+      <c r="P29">
+        <v>0.0830485972</v>
+      </c>
+      <c r="Q29">
+        <v>-0.06795140279999999</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2051740432683794</v>
+      </c>
+      <c r="T29">
+        <v>0.6248541700439469</v>
+      </c>
+      <c r="U29">
+        <v>0.063</v>
+      </c>
+      <c r="V29">
+        <v>0.24</v>
+      </c>
+      <c r="W29">
+        <v>0.04788</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>3.618887525215378</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1639946471079377</v>
+      </c>
+      <c r="C30">
+        <v>2.46873117511184</v>
+      </c>
+      <c r="D30">
+        <v>3.11157117511184</v>
+      </c>
+      <c r="E30">
+        <v>-0.1361599999999999</v>
+      </c>
+      <c r="F30">
+        <v>0.68684</v>
+      </c>
+      <c r="G30">
+        <v>0.044</v>
+      </c>
+      <c r="H30">
+        <v>1.63</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>-0.151</v>
+      </c>
+      <c r="L30">
+        <v>0.151</v>
+      </c>
+      <c r="M30">
+        <v>0.048147484</v>
+      </c>
+      <c r="N30">
+        <v>0.102852516</v>
+      </c>
+      <c r="O30">
+        <v>0.02468460384</v>
+      </c>
+      <c r="P30">
+        <v>0.07816791216000001</v>
+      </c>
+      <c r="Q30">
+        <v>-0.07283208783999999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2070518987610246</v>
+      </c>
+      <c r="T30">
+        <v>0.6319068677621029</v>
+      </c>
+      <c r="U30">
+        <v>0.0701</v>
+      </c>
+      <c r="V30">
+        <v>0.24</v>
+      </c>
+      <c r="W30">
+        <v>0.053276</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>3.13619710637424</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1638277226299584</v>
+      </c>
+      <c r="C31">
+        <v>2.448355432929029</v>
+      </c>
+      <c r="D31">
+        <v>3.115725432929029</v>
+      </c>
+      <c r="E31">
+        <v>-0.11163</v>
+      </c>
+      <c r="F31">
+        <v>0.7113699999999999</v>
+      </c>
+      <c r="G31">
+        <v>0.044</v>
+      </c>
+      <c r="H31">
+        <v>1.63</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>-0.151</v>
+      </c>
+      <c r="L31">
+        <v>0.151</v>
+      </c>
+      <c r="M31">
+        <v>0.049867037</v>
+      </c>
+      <c r="N31">
+        <v>0.101132963</v>
+      </c>
+      <c r="O31">
+        <v>0.02427191112</v>
+      </c>
+      <c r="P31">
+        <v>0.07686105188</v>
+      </c>
+      <c r="Q31">
+        <v>-0.07413894811999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2089826515914908</v>
+      </c>
+      <c r="T31">
+        <v>0.6391582330216155</v>
+      </c>
+      <c r="U31">
+        <v>0.0701</v>
+      </c>
+      <c r="V31">
+        <v>0.24</v>
+      </c>
+      <c r="W31">
+        <v>0.053276</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>3.028052378568231</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1685171981519792</v>
+      </c>
+      <c r="C32">
+        <v>2.311187183265793</v>
+      </c>
+      <c r="D32">
+        <v>3.003087183265793</v>
+      </c>
+      <c r="E32">
+        <v>-0.08710000000000007</v>
+      </c>
+      <c r="F32">
+        <v>0.7358999999999999</v>
+      </c>
+      <c r="G32">
+        <v>0.044</v>
+      </c>
+      <c r="H32">
+        <v>1.63</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>-0.151</v>
+      </c>
+      <c r="L32">
+        <v>0.151</v>
+      </c>
+      <c r="M32">
+        <v>0.06726126</v>
+      </c>
+      <c r="N32">
+        <v>0.08373873999999999</v>
+      </c>
+      <c r="O32">
+        <v>0.0200972976</v>
+      </c>
+      <c r="P32">
+        <v>0.0636414424</v>
+      </c>
+      <c r="Q32">
+        <v>-0.0873585576</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2109685687885417</v>
+      </c>
+      <c r="T32">
+        <v>0.6466167801456852</v>
+      </c>
+      <c r="U32">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V32">
+        <v>0.24</v>
+      </c>
+      <c r="W32">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>2.244977272206913</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1685121536739999</v>
+      </c>
+      <c r="C33">
+        <v>2.28677397268557</v>
+      </c>
+      <c r="D33">
+        <v>3.00320397268557</v>
+      </c>
+      <c r="E33">
+        <v>-0.06257000000000001</v>
+      </c>
+      <c r="F33">
+        <v>0.7604299999999999</v>
+      </c>
+      <c r="G33">
+        <v>0.044</v>
+      </c>
+      <c r="H33">
+        <v>1.63</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>-0.151</v>
+      </c>
+      <c r="L33">
+        <v>0.151</v>
+      </c>
+      <c r="M33">
+        <v>0.069503302</v>
+      </c>
+      <c r="N33">
+        <v>0.08149669799999999</v>
+      </c>
+      <c r="O33">
+        <v>0.01955920752</v>
+      </c>
+      <c r="P33">
+        <v>0.06193749048</v>
+      </c>
+      <c r="Q33">
+        <v>-0.08906250952</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2130120488028985</v>
+      </c>
+      <c r="T33">
+        <v>0.6542915170414675</v>
+      </c>
+      <c r="U33">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V33">
+        <v>0.24</v>
+      </c>
+      <c r="W33">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>2.17255865052282</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1685071091960206</v>
+      </c>
+      <c r="C34">
+        <v>2.262360771189534</v>
+      </c>
+      <c r="D34">
+        <v>3.003320771189534</v>
+      </c>
+      <c r="E34">
+        <v>-0.03803999999999996</v>
+      </c>
+      <c r="F34">
+        <v>0.78496</v>
+      </c>
+      <c r="G34">
+        <v>0.044</v>
+      </c>
+      <c r="H34">
+        <v>1.63</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>-0.151</v>
+      </c>
+      <c r="L34">
+        <v>0.151</v>
+      </c>
+      <c r="M34">
+        <v>0.071745344</v>
+      </c>
+      <c r="N34">
+        <v>0.07925465599999999</v>
+      </c>
+      <c r="O34">
+        <v>0.01902111744</v>
+      </c>
+      <c r="P34">
+        <v>0.06023353855999999</v>
+      </c>
+      <c r="Q34">
+        <v>-0.09076646144</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2151156311706186</v>
+      </c>
+      <c r="T34">
+        <v>0.6621919814930078</v>
+      </c>
+      <c r="U34">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V34">
+        <v>0.24</v>
+      </c>
+      <c r="W34">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>2.104666192693982</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1685020647180414</v>
+      </c>
+      <c r="C35">
+        <v>2.237947578778742</v>
+      </c>
+      <c r="D35">
+        <v>3.003437578778742</v>
+      </c>
+      <c r="E35">
+        <v>-0.01350999999999991</v>
+      </c>
+      <c r="F35">
+        <v>0.80949</v>
+      </c>
+      <c r="G35">
+        <v>0.044</v>
+      </c>
+      <c r="H35">
+        <v>1.63</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>-0.151</v>
+      </c>
+      <c r="L35">
+        <v>0.151</v>
+      </c>
+      <c r="M35">
+        <v>0.07398738600000002</v>
+      </c>
+      <c r="N35">
+        <v>0.07701261399999998</v>
+      </c>
+      <c r="O35">
+        <v>0.01848302735999999</v>
+      </c>
+      <c r="P35">
+        <v>0.05852958663999999</v>
+      </c>
+      <c r="Q35">
+        <v>-0.09247041336</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2172820070418528</v>
+      </c>
+      <c r="T35">
+        <v>0.6703282807042957</v>
+      </c>
+      <c r="U35">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V35">
+        <v>0.24</v>
+      </c>
+      <c r="W35">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>2.040888429279012</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1739492602400622</v>
+      </c>
+      <c r="C36">
+        <v>2.09236392520541</v>
+      </c>
+      <c r="D36">
+        <v>2.88238392520541</v>
+      </c>
+      <c r="E36">
+        <v>0.01102000000000003</v>
+      </c>
+      <c r="F36">
+        <v>0.83402</v>
+      </c>
+      <c r="G36">
+        <v>0.044</v>
+      </c>
+      <c r="H36">
+        <v>1.63</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>-0.151</v>
+      </c>
+      <c r="L36">
+        <v>0.151</v>
+      </c>
+      <c r="M36">
+        <v>0.09382725</v>
+      </c>
+      <c r="N36">
+        <v>0.05717274999999999</v>
+      </c>
+      <c r="O36">
+        <v>0.01372146</v>
+      </c>
+      <c r="P36">
+        <v>0.04345129</v>
+      </c>
+      <c r="Q36">
+        <v>-0.10754871</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2195140306667609</v>
+      </c>
+      <c r="T36">
+        <v>0.6787111344371379</v>
+      </c>
+      <c r="U36">
+        <v>0.1125</v>
+      </c>
+      <c r="V36">
+        <v>0.24</v>
+      </c>
+      <c r="W36">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>1.609340570036956</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1741045757620829</v>
+      </c>
+      <c r="C37">
+        <v>2.064525249490003</v>
+      </c>
+      <c r="D37">
+        <v>2.879075249490003</v>
+      </c>
+      <c r="E37">
+        <v>0.03555000000000008</v>
+      </c>
+      <c r="F37">
+        <v>0.85855</v>
+      </c>
+      <c r="G37">
+        <v>0.044</v>
+      </c>
+      <c r="H37">
+        <v>1.63</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>-0.151</v>
+      </c>
+      <c r="L37">
+        <v>0.151</v>
+      </c>
+      <c r="M37">
+        <v>0.096586875</v>
+      </c>
+      <c r="N37">
+        <v>0.05441312499999999</v>
+      </c>
+      <c r="O37">
+        <v>0.01305915</v>
+      </c>
+      <c r="P37">
+        <v>0.04135397499999999</v>
+      </c>
+      <c r="Q37">
+        <v>-0.109646025</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.221814731941666</v>
+      </c>
+      <c r="T37">
+        <v>0.6873519221309905</v>
+      </c>
+      <c r="U37">
+        <v>0.1125</v>
+      </c>
+      <c r="V37">
+        <v>0.24</v>
+      </c>
+      <c r="W37">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>1.563359410893043</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1742598912841037</v>
+      </c>
+      <c r="C38">
+        <v>2.036694161093484</v>
+      </c>
+      <c r="D38">
+        <v>2.875774161093484</v>
+      </c>
+      <c r="E38">
+        <v>0.06007999999999991</v>
+      </c>
+      <c r="F38">
+        <v>0.8830799999999999</v>
+      </c>
+      <c r="G38">
+        <v>0.044</v>
+      </c>
+      <c r="H38">
+        <v>1.63</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>-0.151</v>
+      </c>
+      <c r="L38">
+        <v>0.151</v>
+      </c>
+      <c r="M38">
+        <v>0.09934649999999999</v>
+      </c>
+      <c r="N38">
+        <v>0.0516535</v>
+      </c>
+      <c r="O38">
+        <v>0.01239684</v>
+      </c>
+      <c r="P38">
+        <v>0.03925666000000001</v>
+      </c>
+      <c r="Q38">
+        <v>-0.11174334</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.224187330131412</v>
+      </c>
+      <c r="T38">
+        <v>0.696262734440276</v>
+      </c>
+      <c r="U38">
+        <v>0.1125</v>
+      </c>
+      <c r="V38">
+        <v>0.24</v>
+      </c>
+      <c r="W38">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>1.519932760590459</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2025216570215649</v>
+      </c>
+      <c r="C39">
+        <v>1.515745683946243</v>
+      </c>
+      <c r="D39">
+        <v>2.379355683946243</v>
+      </c>
+      <c r="E39">
+        <v>0.08460999999999996</v>
+      </c>
+      <c r="F39">
+        <v>0.9076099999999999</v>
+      </c>
+      <c r="G39">
+        <v>0.044</v>
+      </c>
+      <c r="H39">
+        <v>1.63</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>-0.151</v>
+      </c>
+      <c r="L39">
+        <v>0.151</v>
+      </c>
+      <c r="M39">
+        <v>0.178436126</v>
+      </c>
+      <c r="N39">
+        <v>-0.02743612599999998</v>
+      </c>
+      <c r="O39">
+        <v>-0.006584670239999995</v>
+      </c>
+      <c r="P39">
+        <v>-0.02085145575999998</v>
+      </c>
+      <c r="Q39">
+        <v>-0.17185145576</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2294498467531812</v>
+      </c>
+      <c r="T39">
+        <v>0.7160272685673557</v>
+      </c>
+      <c r="U39">
+        <v>0.1966</v>
+      </c>
+      <c r="V39">
+        <v>0.2030978861309733</v>
+      </c>
+      <c r="W39">
+        <v>0.1566709555866506</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.8462411922123887</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2040996570215649</v>
+      </c>
+      <c r="C40">
+        <v>1.468501642447794</v>
+      </c>
+      <c r="D40">
+        <v>2.356641642447794</v>
+      </c>
+      <c r="E40">
+        <v>0.10914</v>
+      </c>
+      <c r="F40">
+        <v>0.93214</v>
+      </c>
+      <c r="G40">
+        <v>0.044</v>
+      </c>
+      <c r="H40">
+        <v>1.63</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>-0.151</v>
+      </c>
+      <c r="L40">
+        <v>0.151</v>
+      </c>
+      <c r="M40">
+        <v>0.183258724</v>
+      </c>
+      <c r="N40">
+        <v>-0.03225872399999999</v>
+      </c>
+      <c r="O40">
+        <v>-0.007742093759999997</v>
+      </c>
+      <c r="P40">
+        <v>-0.02451663023999999</v>
+      </c>
+      <c r="Q40">
+        <v>-0.17551663024</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2325248442814584</v>
+      </c>
+      <c r="T40">
+        <v>0.7275760954797325</v>
+      </c>
+      <c r="U40">
+        <v>0.1966</v>
+      </c>
+      <c r="V40">
+        <v>0.1977532049170003</v>
+      </c>
+      <c r="W40">
+        <v>0.1577217199133177</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.8239716871541679</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2056776570215649</v>
+      </c>
+      <c r="C41">
+        <v>1.421687170229311</v>
+      </c>
+      <c r="D41">
+        <v>2.334357170229311</v>
+      </c>
+      <c r="E41">
+        <v>0.1336700000000001</v>
+      </c>
+      <c r="F41">
+        <v>0.95667</v>
+      </c>
+      <c r="G41">
+        <v>0.044</v>
+      </c>
+      <c r="H41">
+        <v>1.63</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>-0.151</v>
+      </c>
+      <c r="L41">
+        <v>0.151</v>
+      </c>
+      <c r="M41">
+        <v>0.188081322</v>
+      </c>
+      <c r="N41">
+        <v>-0.037081322</v>
+      </c>
+      <c r="O41">
+        <v>-0.00889951728</v>
+      </c>
+      <c r="P41">
+        <v>-0.02818180472</v>
+      </c>
+      <c r="Q41">
+        <v>-0.17918180472</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2357006614008265</v>
+      </c>
+      <c r="T41">
+        <v>0.7395035724548099</v>
+      </c>
+      <c r="U41">
+        <v>0.1966</v>
+      </c>
+      <c r="V41">
+        <v>0.1926826099191285</v>
+      </c>
+      <c r="W41">
+        <v>0.1587185988898993</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.8028442079963687</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2149207693669057</v>
+      </c>
+      <c r="C42">
+        <v>1.27464620428167</v>
+      </c>
+      <c r="D42">
+        <v>2.211846204281669</v>
+      </c>
+      <c r="E42">
+        <v>0.1582</v>
+      </c>
+      <c r="F42">
+        <v>0.9812</v>
+      </c>
+      <c r="G42">
+        <v>0.044</v>
+      </c>
+      <c r="H42">
+        <v>1.63</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>-0.151</v>
+      </c>
+      <c r="L42">
+        <v>0.151</v>
+      </c>
+      <c r="M42">
+        <v>0.20978056</v>
+      </c>
+      <c r="N42">
+        <v>-0.05878055999999998</v>
+      </c>
+      <c r="O42">
+        <v>-0.0141073344</v>
+      </c>
+      <c r="P42">
+        <v>-0.04467322559999998</v>
+      </c>
+      <c r="Q42">
+        <v>-0.1956732256</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2402908596664083</v>
+      </c>
+      <c r="T42">
+        <v>0.7567430676983713</v>
+      </c>
+      <c r="U42">
+        <v>0.2138</v>
+      </c>
+      <c r="V42">
+        <v>0.1727519461288501</v>
+      </c>
+      <c r="W42">
+        <v>0.1768656339176519</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.7197997755368754</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2166707693669057</v>
+      </c>
+      <c r="C43">
+        <v>1.228354726151958</v>
+      </c>
+      <c r="D43">
+        <v>2.190084726151958</v>
+      </c>
+      <c r="E43">
+        <v>0.1827300000000001</v>
+      </c>
+      <c r="F43">
+        <v>1.00573</v>
+      </c>
+      <c r="G43">
+        <v>0.044</v>
+      </c>
+      <c r="H43">
+        <v>1.63</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>-0.151</v>
+      </c>
+      <c r="L43">
+        <v>0.151</v>
+      </c>
+      <c r="M43">
+        <v>0.215025074</v>
+      </c>
+      <c r="N43">
+        <v>-0.06402507399999999</v>
+      </c>
+      <c r="O43">
+        <v>-0.01536601776</v>
+      </c>
+      <c r="P43">
+        <v>-0.04865905623999999</v>
+      </c>
+      <c r="Q43">
+        <v>-0.19965905624</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2437059589827882</v>
+      </c>
+      <c r="T43">
+        <v>0.7695692213881743</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.1685384840281464</v>
+      </c>
+      <c r="W43">
+        <v>0.1777664721147823</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.7022436834506101</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2184207693669057</v>
+      </c>
+      <c r="C44">
+        <v>1.182487281243585</v>
+      </c>
+      <c r="D44">
+        <v>2.168747281243585</v>
+      </c>
+      <c r="E44">
+        <v>0.20726</v>
+      </c>
+      <c r="F44">
+        <v>1.03026</v>
+      </c>
+      <c r="G44">
+        <v>0.044</v>
+      </c>
+      <c r="H44">
+        <v>1.63</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>-0.151</v>
+      </c>
+      <c r="L44">
+        <v>0.151</v>
+      </c>
+      <c r="M44">
+        <v>0.220269588</v>
+      </c>
+      <c r="N44">
+        <v>-0.06926958799999999</v>
+      </c>
+      <c r="O44">
+        <v>-0.01662470112</v>
+      </c>
+      <c r="P44">
+        <v>-0.05264488687999999</v>
+      </c>
+      <c r="Q44">
+        <v>-0.20364488688</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2472388203445603</v>
+      </c>
+      <c r="T44">
+        <v>0.7828376562396944</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.1645256629798572</v>
+      </c>
+      <c r="W44">
+        <v>0.1786244132549065</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.685523595749405</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2201707693669058</v>
+      </c>
+      <c r="C45">
+        <v>1.13703159539341</v>
+      </c>
+      <c r="D45">
+        <v>2.14782159539341</v>
+      </c>
+      <c r="E45">
+        <v>0.2317899999999999</v>
+      </c>
+      <c r="F45">
+        <v>1.05479</v>
+      </c>
+      <c r="G45">
+        <v>0.044</v>
+      </c>
+      <c r="H45">
+        <v>1.63</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>-0.151</v>
+      </c>
+      <c r="L45">
+        <v>0.151</v>
+      </c>
+      <c r="M45">
+        <v>0.225514102</v>
+      </c>
+      <c r="N45">
+        <v>-0.07451410199999997</v>
+      </c>
+      <c r="O45">
+        <v>-0.01788338447999999</v>
+      </c>
+      <c r="P45">
+        <v>-0.05663071751999998</v>
+      </c>
+      <c r="Q45">
+        <v>-0.20763071752</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2508956417541141</v>
+      </c>
+      <c r="T45">
+        <v>0.7965716502088118</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0.1606994847710233</v>
+      </c>
+      <c r="W45">
+        <v>0.1794424501559552</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.6695811865459306</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2219207693669058</v>
+      </c>
+      <c r="C46">
+        <v>1.091975863632162</v>
+      </c>
+      <c r="D46">
+        <v>2.127295863632162</v>
+      </c>
+      <c r="E46">
+        <v>0.2563199999999999</v>
+      </c>
+      <c r="F46">
+        <v>1.07932</v>
+      </c>
+      <c r="G46">
+        <v>0.044</v>
+      </c>
+      <c r="H46">
+        <v>1.63</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>-0.151</v>
+      </c>
+      <c r="L46">
+        <v>0.151</v>
+      </c>
+      <c r="M46">
+        <v>0.2307586159999999</v>
+      </c>
+      <c r="N46">
+        <v>-0.07975861599999995</v>
+      </c>
+      <c r="O46">
+        <v>-0.01914206783999999</v>
+      </c>
+      <c r="P46">
+        <v>-0.06061654815999996</v>
+      </c>
+      <c r="Q46">
+        <v>-0.21161654816</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2546830639282947</v>
+      </c>
+      <c r="T46">
+        <v>0.8107961439625406</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.1570472237535001</v>
+      </c>
+      <c r="W46">
+        <v>0.1802233035615017</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.6543634323062504</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2236707693669057</v>
+      </c>
+      <c r="C47">
+        <v>1.047308727977321</v>
+      </c>
+      <c r="D47">
+        <v>2.107158727977321</v>
+      </c>
+      <c r="E47">
+        <v>0.28085</v>
+      </c>
+      <c r="F47">
+        <v>1.10385</v>
+      </c>
+      <c r="G47">
+        <v>0.044</v>
+      </c>
+      <c r="H47">
+        <v>1.63</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>-0.151</v>
+      </c>
+      <c r="L47">
+        <v>0.151</v>
+      </c>
+      <c r="M47">
+        <v>0.23600313</v>
+      </c>
+      <c r="N47">
+        <v>-0.08500312999999998</v>
+      </c>
+      <c r="O47">
+        <v>-0.02040075119999999</v>
+      </c>
+      <c r="P47">
+        <v>-0.06460237879999998</v>
+      </c>
+      <c r="Q47">
+        <v>-0.2156023788</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2586082105451727</v>
+      </c>
+      <c r="T47">
+        <v>0.8255378920345868</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.1535572854478667</v>
+      </c>
+      <c r="W47">
+        <v>0.1809694523712461</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.6398220226994448</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2254207693669057</v>
+      </c>
+      <c r="C48">
+        <v>1.003019256475462</v>
+      </c>
+      <c r="D48">
+        <v>2.087399256475462</v>
+      </c>
+      <c r="E48">
+        <v>0.30538</v>
+      </c>
+      <c r="F48">
+        <v>1.12838</v>
+      </c>
+      <c r="G48">
+        <v>0.044</v>
+      </c>
+      <c r="H48">
+        <v>1.63</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>-0.151</v>
+      </c>
+      <c r="L48">
+        <v>0.151</v>
+      </c>
+      <c r="M48">
+        <v>0.241247644</v>
+      </c>
+      <c r="N48">
+        <v>-0.09024764399999999</v>
+      </c>
+      <c r="O48">
+        <v>-0.02165943456</v>
+      </c>
+      <c r="P48">
+        <v>-0.06858820943999999</v>
+      </c>
+      <c r="Q48">
+        <v>-0.21958820944</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2626787329626759</v>
+      </c>
+      <c r="T48">
+        <v>0.8408256307759681</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.1502190835903044</v>
+      </c>
+      <c r="W48">
+        <v>0.1816831599283929</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.625912848292935</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2271707693669058</v>
+      </c>
+      <c r="C49">
+        <v>0.9590969234128048</v>
+      </c>
+      <c r="D49">
+        <v>2.068006923412805</v>
+      </c>
+      <c r="E49">
+        <v>0.3299100000000001</v>
+      </c>
+      <c r="F49">
+        <v>1.15291</v>
+      </c>
+      <c r="G49">
+        <v>0.044</v>
+      </c>
+      <c r="H49">
+        <v>1.63</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>-0.151</v>
+      </c>
+      <c r="L49">
+        <v>0.151</v>
+      </c>
+      <c r="M49">
+        <v>0.246492158</v>
+      </c>
+      <c r="N49">
+        <v>-0.09549215800000002</v>
+      </c>
+      <c r="O49">
+        <v>-0.02291811792000001</v>
+      </c>
+      <c r="P49">
+        <v>-0.07257404008000001</v>
+      </c>
+      <c r="Q49">
+        <v>-0.22357404008</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2669028599997075</v>
+      </c>
+      <c r="T49">
+        <v>0.8566902653189109</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0.1470229328756171</v>
+      </c>
+      <c r="W49">
+        <v>0.1823664969511931</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.6125955536484045</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2289207693669057</v>
+      </c>
+      <c r="C50">
+        <v>0.9155315906186896</v>
+      </c>
+      <c r="D50">
+        <v>2.048971590618689</v>
+      </c>
+      <c r="E50">
+        <v>0.3544399999999999</v>
+      </c>
+      <c r="F50">
+        <v>1.17744</v>
+      </c>
+      <c r="G50">
+        <v>0.044</v>
+      </c>
+      <c r="H50">
+        <v>1.63</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>-0.151</v>
+      </c>
+      <c r="L50">
+        <v>0.151</v>
+      </c>
+      <c r="M50">
+        <v>0.2517366719999999</v>
+      </c>
+      <c r="N50">
+        <v>-0.1007366719999999</v>
+      </c>
+      <c r="O50">
+        <v>-0.02417680127999999</v>
+      </c>
+      <c r="P50">
+        <v>-0.07655987071999995</v>
+      </c>
+      <c r="Q50">
+        <v>-0.2275598707199999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2712894534612403</v>
+      </c>
+      <c r="T50">
+        <v>0.8731650781135053</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.1439599551073751</v>
+      </c>
+      <c r="W50">
+        <v>0.1830213615980432</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.5998331462807296</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2306707693669057</v>
+      </c>
+      <c r="C51">
+        <v>0.8723134897922107</v>
+      </c>
+      <c r="D51">
+        <v>2.030283489792211</v>
+      </c>
+      <c r="E51">
+        <v>0.37897</v>
+      </c>
+      <c r="F51">
+        <v>1.20197</v>
+      </c>
+      <c r="G51">
+        <v>0.044</v>
+      </c>
+      <c r="H51">
+        <v>1.63</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>-0.151</v>
+      </c>
+      <c r="L51">
+        <v>0.151</v>
+      </c>
+      <c r="M51">
+        <v>0.256981186</v>
+      </c>
+      <c r="N51">
+        <v>-0.105981186</v>
+      </c>
+      <c r="O51">
+        <v>-0.02543548464</v>
+      </c>
+      <c r="P51">
+        <v>-0.08054570135999999</v>
+      </c>
+      <c r="Q51">
+        <v>-0.23154570136</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2758480701957745</v>
+      </c>
+      <c r="T51">
+        <v>0.8902859619980839</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0.1410219968398776</v>
+      </c>
+      <c r="W51">
+        <v>0.1836494970756342</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.5875916534994901</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2324207693669057</v>
+      </c>
+      <c r="C52">
+        <v>0.829433205787278</v>
+      </c>
+      <c r="D52">
+        <v>2.011933205787278</v>
+      </c>
+      <c r="E52">
+        <v>0.4035</v>
+      </c>
+      <c r="F52">
+        <v>1.2265</v>
+      </c>
+      <c r="G52">
+        <v>0.044</v>
+      </c>
+      <c r="H52">
+        <v>1.63</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>-0.151</v>
+      </c>
+      <c r="L52">
+        <v>0.151</v>
+      </c>
+      <c r="M52">
+        <v>0.2622257</v>
+      </c>
+      <c r="N52">
+        <v>-0.1112257</v>
+      </c>
+      <c r="O52">
+        <v>-0.02669416799999999</v>
+      </c>
+      <c r="P52">
+        <v>-0.08453153199999996</v>
+      </c>
+      <c r="Q52">
+        <v>-0.235531532</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.28058903159969</v>
+      </c>
+      <c r="T52">
+        <v>0.9080916812380455</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0.1382015569030801</v>
+      </c>
+      <c r="W52">
+        <v>0.1842525071341215</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.5758398204295003</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2341707693669058</v>
+      </c>
+      <c r="C53">
+        <v>0.7868816607959921</v>
+      </c>
+      <c r="D53">
+        <v>1.993911660795992</v>
+      </c>
+      <c r="E53">
+        <v>0.4280299999999999</v>
+      </c>
+      <c r="F53">
+        <v>1.25103</v>
+      </c>
+      <c r="G53">
+        <v>0.044</v>
+      </c>
+      <c r="H53">
+        <v>1.63</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>-0.151</v>
+      </c>
+      <c r="L53">
+        <v>0.151</v>
+      </c>
+      <c r="M53">
+        <v>0.267470214</v>
+      </c>
+      <c r="N53">
+        <v>-0.116470214</v>
+      </c>
+      <c r="O53">
+        <v>-0.02795285136</v>
+      </c>
+      <c r="P53">
+        <v>-0.08851736263999999</v>
+      </c>
+      <c r="Q53">
+        <v>-0.23951736264</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2855235016323368</v>
+      </c>
+      <c r="T53">
+        <v>0.926624164528618</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0.135491722454</v>
+      </c>
+      <c r="W53">
+        <v>0.1848318697393348</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.5645488435583336</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2359207693669057</v>
+      </c>
+      <c r="C54">
+        <v>0.7446500993745357</v>
+      </c>
+      <c r="D54">
+        <v>1.976210099374536</v>
+      </c>
+      <c r="E54">
+        <v>0.4525600000000001</v>
+      </c>
+      <c r="F54">
+        <v>1.27556</v>
+      </c>
+      <c r="G54">
+        <v>0.044</v>
+      </c>
+      <c r="H54">
+        <v>1.63</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>-0.151</v>
+      </c>
+      <c r="L54">
+        <v>0.151</v>
+      </c>
+      <c r="M54">
+        <v>0.272714728</v>
+      </c>
+      <c r="N54">
+        <v>-0.121714728</v>
+      </c>
+      <c r="O54">
+        <v>-0.02921153472</v>
+      </c>
+      <c r="P54">
+        <v>-0.09250319328000002</v>
+      </c>
+      <c r="Q54">
+        <v>-0.24350319328</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2906635745830104</v>
+      </c>
+      <c r="T54">
+        <v>0.9459288346229641</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0.1328861124068077</v>
+      </c>
+      <c r="W54">
+        <v>0.1853889491674245</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.5536921350283656</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2376707693669057</v>
+      </c>
+      <c r="C55">
+        <v>0.7027300742596587</v>
+      </c>
+      <c r="D55">
+        <v>1.958820074259659</v>
+      </c>
+      <c r="E55">
+        <v>0.47709</v>
+      </c>
+      <c r="F55">
+        <v>1.30009</v>
+      </c>
+      <c r="G55">
+        <v>0.044</v>
+      </c>
+      <c r="H55">
+        <v>1.63</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>-0.151</v>
+      </c>
+      <c r="L55">
+        <v>0.151</v>
+      </c>
+      <c r="M55">
+        <v>0.277959242</v>
+      </c>
+      <c r="N55">
+        <v>-0.126959242</v>
+      </c>
+      <c r="O55">
+        <v>-0.03047021808</v>
+      </c>
+      <c r="P55">
+        <v>-0.09648902392</v>
+      </c>
+      <c r="Q55">
+        <v>-0.24748902392</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2960223740422234</v>
+      </c>
+      <c r="T55">
+        <v>0.966054980040474</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.1303788272670567</v>
+      </c>
+      <c r="W55">
+        <v>0.1859250067303033</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.5432451136127361</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2394207693669057</v>
+      </c>
+      <c r="C56">
+        <v>0.6611134329274984</v>
+      </c>
+      <c r="D56">
+        <v>1.941733432927498</v>
+      </c>
+      <c r="E56">
+        <v>0.50162</v>
+      </c>
+      <c r="F56">
+        <v>1.32462</v>
+      </c>
+      <c r="G56">
+        <v>0.044</v>
+      </c>
+      <c r="H56">
+        <v>1.63</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>-0.151</v>
+      </c>
+      <c r="L56">
+        <v>0.151</v>
+      </c>
+      <c r="M56">
+        <v>0.283203756</v>
+      </c>
+      <c r="N56">
+        <v>-0.132203756</v>
+      </c>
+      <c r="O56">
+        <v>-0.03172890143999999</v>
+      </c>
+      <c r="P56">
+        <v>-0.10047485456</v>
+      </c>
+      <c r="Q56">
+        <v>-0.25147485456</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.3016141647822717</v>
+      </c>
+      <c r="T56">
+        <v>0.9870561752587451</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0.1279644045398889</v>
+      </c>
+      <c r="W56">
+        <v>0.1864412103093717</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.533185018916204</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2411707693669057</v>
+      </c>
+      <c r="C57">
+        <v>0.6197923048497946</v>
+      </c>
+      <c r="D57">
+        <v>1.924942304849795</v>
+      </c>
+      <c r="E57">
+        <v>0.5261500000000001</v>
+      </c>
+      <c r="F57">
+        <v>1.34915</v>
+      </c>
+      <c r="G57">
+        <v>0.044</v>
+      </c>
+      <c r="H57">
+        <v>1.63</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>-0.151</v>
+      </c>
+      <c r="L57">
+        <v>0.151</v>
+      </c>
+      <c r="M57">
+        <v>0.28844827</v>
+      </c>
+      <c r="N57">
+        <v>-0.13744827</v>
+      </c>
+      <c r="O57">
+        <v>-0.0329875848</v>
+      </c>
+      <c r="P57">
+        <v>-0.1044606852</v>
+      </c>
+      <c r="Q57">
+        <v>-0.2554606852</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.3074544795552112</v>
+      </c>
+      <c r="T57">
+        <v>1.008990756931162</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.1256377790028</v>
+      </c>
+      <c r="W57">
+        <v>0.1869386428492013</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.5234907458450002</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2429207693669057</v>
+      </c>
+      <c r="C58">
+        <v>0.5787590894056478</v>
+      </c>
+      <c r="D58">
+        <v>1.908439089405648</v>
+      </c>
+      <c r="E58">
+        <v>0.5506800000000001</v>
+      </c>
+      <c r="F58">
+        <v>1.37368</v>
+      </c>
+      <c r="G58">
+        <v>0.044</v>
+      </c>
+      <c r="H58">
+        <v>1.63</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>-0.151</v>
+      </c>
+      <c r="L58">
+        <v>0.151</v>
+      </c>
+      <c r="M58">
+        <v>0.293692784</v>
+      </c>
+      <c r="N58">
+        <v>-0.142692784</v>
+      </c>
+      <c r="O58">
+        <v>-0.03424626816</v>
+      </c>
+      <c r="P58">
+        <v>-0.10844651584</v>
+      </c>
+      <c r="Q58">
+        <v>-0.25944651584</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.3135602631814659</v>
+      </c>
+      <c r="T58">
+        <v>1.031922365043234</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.1233942472348929</v>
+      </c>
+      <c r="W58">
+        <v>0.1874183099411799</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.5141426968120537</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2446707693669058</v>
+      </c>
+      <c r="C59">
+        <v>0.5380064444098067</v>
+      </c>
+      <c r="D59">
+        <v>1.892216444409807</v>
+      </c>
+      <c r="E59">
+        <v>0.5752100000000002</v>
+      </c>
+      <c r="F59">
+        <v>1.39821</v>
+      </c>
+      <c r="G59">
+        <v>0.044</v>
+      </c>
+      <c r="H59">
+        <v>1.63</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>-0.151</v>
+      </c>
+      <c r="L59">
+        <v>0.151</v>
+      </c>
+      <c r="M59">
+        <v>0.298937298</v>
+      </c>
+      <c r="N59">
+        <v>-0.147937298</v>
+      </c>
+      <c r="O59">
+        <v>-0.03550495152</v>
+      </c>
+      <c r="P59">
+        <v>-0.11243234648</v>
+      </c>
+      <c r="Q59">
+        <v>-0.26343234648</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3199500367438257</v>
+      </c>
+      <c r="T59">
+        <v>1.055920559579123</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.1212294358798948</v>
+      </c>
+      <c r="W59">
+        <v>0.1878811466088785</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.5051226494995615</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2618602602265699</v>
+      </c>
+      <c r="C60">
+        <v>0.3676582818977998</v>
+      </c>
+      <c r="D60">
+        <v>1.7463982818978</v>
+      </c>
+      <c r="E60">
+        <v>0.5997399999999999</v>
+      </c>
+      <c r="F60">
+        <v>1.42274</v>
+      </c>
+      <c r="G60">
+        <v>0.044</v>
+      </c>
+      <c r="H60">
+        <v>1.63</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>-0.151</v>
+      </c>
+      <c r="L60">
+        <v>0.151</v>
+      </c>
+      <c r="M60">
+        <v>0.339750312</v>
+      </c>
+      <c r="N60">
+        <v>-0.188750312</v>
+      </c>
+      <c r="O60">
+        <v>-0.04530007488</v>
+      </c>
+      <c r="P60">
+        <v>-0.14345023712</v>
+      </c>
+      <c r="Q60">
+        <v>-0.29445023712</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3288809682369265</v>
+      </c>
+      <c r="T60">
+        <v>1.089462629461015</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.1066665687123784</v>
+      </c>
+      <c r="W60">
+        <v>0.213328023391484</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.4444440363015767</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2638602602265699</v>
+      </c>
+      <c r="C61">
+        <v>0.327608898065757</v>
+      </c>
+      <c r="D61">
+        <v>1.730878898065757</v>
+      </c>
+      <c r="E61">
+        <v>0.6242699999999999</v>
+      </c>
+      <c r="F61">
+        <v>1.44727</v>
+      </c>
+      <c r="G61">
+        <v>0.044</v>
+      </c>
+      <c r="H61">
+        <v>1.63</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>-0.151</v>
+      </c>
+      <c r="L61">
+        <v>0.151</v>
+      </c>
+      <c r="M61">
+        <v>0.345608076</v>
+      </c>
+      <c r="N61">
+        <v>-0.194608076</v>
+      </c>
+      <c r="O61">
+        <v>-0.04670593823999999</v>
+      </c>
+      <c r="P61">
+        <v>-0.14790213776</v>
+      </c>
+      <c r="Q61">
+        <v>-0.29890213776</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3359561138036808</v>
+      </c>
+      <c r="T61">
+        <v>1.116034888716162</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.1048586607681008</v>
+      </c>
+      <c r="W61">
+        <v>0.2137597518085775</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.4369110865337533</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2658602602265699</v>
+      </c>
+      <c r="C62">
+        <v>0.28783291097547</v>
+      </c>
+      <c r="D62">
+        <v>1.71563291097547</v>
+      </c>
+      <c r="E62">
+        <v>0.6487999999999998</v>
+      </c>
+      <c r="F62">
+        <v>1.4718</v>
+      </c>
+      <c r="G62">
+        <v>0.044</v>
+      </c>
+      <c r="H62">
+        <v>1.63</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>-0.151</v>
+      </c>
+      <c r="L62">
+        <v>0.151</v>
+      </c>
+      <c r="M62">
+        <v>0.35146584</v>
+      </c>
+      <c r="N62">
+        <v>-0.20046584</v>
+      </c>
+      <c r="O62">
+        <v>-0.04811180159999999</v>
+      </c>
+      <c r="P62">
+        <v>-0.1523540384</v>
+      </c>
+      <c r="Q62">
+        <v>-0.3033540384</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.3433850166487729</v>
+      </c>
+      <c r="T62">
+        <v>1.143935760934066</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.1031110164219658</v>
+      </c>
+      <c r="W62">
+        <v>0.2141770892784346</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.4296292350915242</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2678602602265699</v>
+      </c>
+      <c r="C63">
+        <v>0.2483231592780037</v>
+      </c>
+      <c r="D63">
+        <v>1.700653159278004</v>
+      </c>
+      <c r="E63">
+        <v>0.67333</v>
+      </c>
+      <c r="F63">
+        <v>1.49633</v>
+      </c>
+      <c r="G63">
+        <v>0.044</v>
+      </c>
+      <c r="H63">
+        <v>1.63</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>-0.151</v>
+      </c>
+      <c r="L63">
+        <v>0.151</v>
+      </c>
+      <c r="M63">
+        <v>0.357323604</v>
+      </c>
+      <c r="N63">
+        <v>-0.206323604</v>
+      </c>
+      <c r="O63">
+        <v>-0.04951766496000001</v>
+      </c>
+      <c r="P63">
+        <v>-0.15680593904</v>
+      </c>
+      <c r="Q63">
+        <v>-0.30780593904</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3511948888705362</v>
+      </c>
+      <c r="T63">
+        <v>1.173267447111862</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.1014206718904581</v>
+      </c>
+      <c r="W63">
+        <v>0.2145807435525586</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.4225861328769089</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2698602602265698</v>
+      </c>
+      <c r="C64">
+        <v>0.209072729571828</v>
+      </c>
+      <c r="D64">
+        <v>1.685932729571828</v>
+      </c>
+      <c r="E64">
+        <v>0.6978599999999999</v>
+      </c>
+      <c r="F64">
+        <v>1.52086</v>
+      </c>
+      <c r="G64">
+        <v>0.044</v>
+      </c>
+      <c r="H64">
+        <v>1.63</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>-0.151</v>
+      </c>
+      <c r="L64">
+        <v>0.151</v>
+      </c>
+      <c r="M64">
+        <v>0.363181368</v>
+      </c>
+      <c r="N64">
+        <v>-0.212181368</v>
+      </c>
+      <c r="O64">
+        <v>-0.05092352832</v>
+      </c>
+      <c r="P64">
+        <v>-0.16125783968</v>
+      </c>
+      <c r="Q64">
+        <v>-0.31225783968</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3594158069987082</v>
+      </c>
+      <c r="T64">
+        <v>1.204142906246385</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.09978485460190237</v>
+      </c>
+      <c r="W64">
+        <v>0.2149713767210657</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.4157702275079266</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2718602602265699</v>
+      </c>
+      <c r="C65">
+        <v>0.1700749457640449</v>
+      </c>
+      <c r="D65">
+        <v>1.671464945764045</v>
+      </c>
+      <c r="E65">
+        <v>0.7223899999999999</v>
+      </c>
+      <c r="F65">
+        <v>1.54539</v>
+      </c>
+      <c r="G65">
+        <v>0.044</v>
+      </c>
+      <c r="H65">
+        <v>1.63</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>-0.151</v>
+      </c>
+      <c r="L65">
+        <v>0.151</v>
+      </c>
+      <c r="M65">
+        <v>0.369039132</v>
+      </c>
+      <c r="N65">
+        <v>-0.218039132</v>
+      </c>
+      <c r="O65">
+        <v>-0.05232939168</v>
+      </c>
+      <c r="P65">
+        <v>-0.16570974032</v>
+      </c>
+      <c r="Q65">
+        <v>-0.31670974032</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3680810990797544</v>
+      </c>
+      <c r="T65">
+        <v>1.236687309117909</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.09820096802091979</v>
+      </c>
+      <c r="W65">
+        <v>0.2153496088366044</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.4091707000871658</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.27386026022657</v>
+      </c>
+      <c r="C66">
+        <v>0.131323358974742</v>
+      </c>
+      <c r="D66">
+        <v>1.657243358974742</v>
+      </c>
+      <c r="E66">
+        <v>0.74692</v>
+      </c>
+      <c r="F66">
+        <v>1.56992</v>
+      </c>
+      <c r="G66">
+        <v>0.044</v>
+      </c>
+      <c r="H66">
+        <v>1.63</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>-0.151</v>
+      </c>
+      <c r="L66">
+        <v>0.151</v>
+      </c>
+      <c r="M66">
+        <v>0.374896896</v>
+      </c>
+      <c r="N66">
+        <v>-0.223896896</v>
+      </c>
+      <c r="O66">
+        <v>-0.05373525504000001</v>
+      </c>
+      <c r="P66">
+        <v>-0.17016164096</v>
+      </c>
+      <c r="Q66">
+        <v>-0.32116164096</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3772277962764143</v>
+      </c>
+      <c r="T66">
+        <v>1.271039734371184</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.09666657789559291</v>
+      </c>
+      <c r="W66">
+        <v>0.2157160211985324</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.4027774078983039</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2758602602265699</v>
+      </c>
+      <c r="C67">
+        <v>0.09281173795238473</v>
+      </c>
+      <c r="D67">
+        <v>1.643261737952385</v>
+      </c>
+      <c r="E67">
+        <v>0.77145</v>
+      </c>
+      <c r="F67">
+        <v>1.59445</v>
+      </c>
+      <c r="G67">
+        <v>0.044</v>
+      </c>
+      <c r="H67">
+        <v>1.63</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>-0.151</v>
+      </c>
+      <c r="L67">
+        <v>0.151</v>
+      </c>
+      <c r="M67">
+        <v>0.38075466</v>
+      </c>
+      <c r="N67">
+        <v>-0.22975466</v>
+      </c>
+      <c r="O67">
+        <v>-0.0551411184</v>
+      </c>
+      <c r="P67">
+        <v>-0.1746135416</v>
+      </c>
+      <c r="Q67">
+        <v>-0.3256135416</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3868971618843118</v>
+      </c>
+      <c r="T67">
+        <v>1.307355155353218</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.09517939977412225</v>
+      </c>
+      <c r="W67">
+        <v>0.2160711593339396</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3965808323921761</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2778602602265699</v>
+      </c>
+      <c r="C68">
+        <v>0.05453405997031413</v>
+      </c>
+      <c r="D68">
+        <v>1.629514059970314</v>
+      </c>
+      <c r="E68">
+        <v>0.7959800000000001</v>
+      </c>
+      <c r="F68">
+        <v>1.61898</v>
+      </c>
+      <c r="G68">
+        <v>0.044</v>
+      </c>
+      <c r="H68">
+        <v>1.63</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>-0.151</v>
+      </c>
+      <c r="L68">
+        <v>0.151</v>
+      </c>
+      <c r="M68">
+        <v>0.3866124240000001</v>
+      </c>
+      <c r="N68">
+        <v>-0.2356124240000001</v>
+      </c>
+      <c r="O68">
+        <v>-0.05654698176000002</v>
+      </c>
+      <c r="P68">
+        <v>-0.17906544224</v>
+      </c>
+      <c r="Q68">
+        <v>-0.33006544224</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3971353137044387</v>
+      </c>
+      <c r="T68">
+        <v>1.345806777569489</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.09373728765633252</v>
+      </c>
+      <c r="W68">
+        <v>0.2164155357076678</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3905720319013855</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.27986026022657</v>
+      </c>
+      <c r="C69">
+        <v>0.01648450217643482</v>
+      </c>
+      <c r="D69">
+        <v>1.615994502176435</v>
+      </c>
+      <c r="E69">
+        <v>0.8205100000000001</v>
+      </c>
+      <c r="F69">
+        <v>1.64351</v>
+      </c>
+      <c r="G69">
+        <v>0.044</v>
+      </c>
+      <c r="H69">
+        <v>1.63</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>-0.151</v>
+      </c>
+      <c r="L69">
+        <v>0.151</v>
+      </c>
+      <c r="M69">
+        <v>0.3924701880000001</v>
+      </c>
+      <c r="N69">
+        <v>-0.2414701880000001</v>
+      </c>
+      <c r="O69">
+        <v>-0.05795284512000001</v>
+      </c>
+      <c r="P69">
+        <v>-0.18351734288</v>
+      </c>
+      <c r="Q69">
+        <v>-0.33451734288</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.4079939595742701</v>
+      </c>
+      <c r="T69">
+        <v>1.386588801132201</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.09233822366146188</v>
+      </c>
+      <c r="W69">
+        <v>0.2167496321896429</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3847425985894245</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2818602602265699</v>
+      </c>
+      <c r="C70">
+        <v>-0.02134256663004153</v>
+      </c>
+      <c r="D70">
+        <v>1.602697433369958</v>
+      </c>
+      <c r="E70">
+        <v>0.84504</v>
+      </c>
+      <c r="F70">
+        <v>1.66804</v>
+      </c>
+      <c r="G70">
+        <v>0.044</v>
+      </c>
+      <c r="H70">
+        <v>1.63</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>-0.151</v>
+      </c>
+      <c r="L70">
+        <v>0.151</v>
+      </c>
+      <c r="M70">
+        <v>0.398327952</v>
+      </c>
+      <c r="N70">
+        <v>-0.247327952</v>
+      </c>
+      <c r="O70">
+        <v>-0.05935870847999999</v>
+      </c>
+      <c r="P70">
+        <v>-0.18796924352</v>
+      </c>
+      <c r="Q70">
+        <v>-0.33896924352</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.4195312708109661</v>
+      </c>
+      <c r="T70">
+        <v>1.429919701167582</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.09098030860761687</v>
+      </c>
+      <c r="W70">
+        <v>0.2170739023045011</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3790846191984036</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2838602602265699</v>
+      </c>
+      <c r="C71">
+        <v>-0.05895259381917639</v>
+      </c>
+      <c r="D71">
+        <v>1.589617406180824</v>
+      </c>
+      <c r="E71">
+        <v>0.8695700000000002</v>
+      </c>
+      <c r="F71">
+        <v>1.69257</v>
+      </c>
+      <c r="G71">
+        <v>0.044</v>
+      </c>
+      <c r="H71">
+        <v>1.63</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>-0.151</v>
+      </c>
+      <c r="L71">
+        <v>0.151</v>
+      </c>
+      <c r="M71">
+        <v>0.404185716</v>
+      </c>
+      <c r="N71">
+        <v>-0.2531857160000001</v>
+      </c>
+      <c r="O71">
+        <v>-0.06076457184000001</v>
+      </c>
+      <c r="P71">
+        <v>-0.1924211441600001</v>
+      </c>
+      <c r="Q71">
+        <v>-0.34342114416</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.4318129247080941</v>
+      </c>
+      <c r="T71">
+        <v>1.47604614314073</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.08966175341040503</v>
+      </c>
+      <c r="W71">
+        <v>0.2173887732855953</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3735906392100209</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2858602602265699</v>
+      </c>
+      <c r="C72">
+        <v>-0.09635085037102309</v>
+      </c>
+      <c r="D72">
+        <v>1.576749149628977</v>
+      </c>
+      <c r="E72">
+        <v>0.8941000000000001</v>
+      </c>
+      <c r="F72">
+        <v>1.7171</v>
+      </c>
+      <c r="G72">
+        <v>0.044</v>
+      </c>
+      <c r="H72">
+        <v>1.63</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>-0.151</v>
+      </c>
+      <c r="L72">
+        <v>0.151</v>
+      </c>
+      <c r="M72">
+        <v>0.41004348</v>
+      </c>
+      <c r="N72">
+        <v>-0.25904348</v>
+      </c>
+      <c r="O72">
+        <v>-0.0621704352</v>
+      </c>
+      <c r="P72">
+        <v>-0.1968730448</v>
+      </c>
+      <c r="Q72">
+        <v>-0.3478730448</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.4449133555316972</v>
+      </c>
+      <c r="T72">
+        <v>1.525247681245421</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.0883808712188278</v>
+      </c>
+      <c r="W72">
+        <v>0.2176946479529439</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3682536300784492</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2878602602265699</v>
+      </c>
+      <c r="C73">
+        <v>-0.1335424379578551</v>
+      </c>
+      <c r="D73">
+        <v>1.564087562042145</v>
+      </c>
+      <c r="E73">
+        <v>0.9186299999999998</v>
+      </c>
+      <c r="F73">
+        <v>1.74163</v>
+      </c>
+      <c r="G73">
+        <v>0.044</v>
+      </c>
+      <c r="H73">
+        <v>1.63</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>-0.151</v>
+      </c>
+      <c r="L73">
+        <v>0.151</v>
+      </c>
+      <c r="M73">
+        <v>0.4159012439999999</v>
+      </c>
+      <c r="N73">
+        <v>-0.2649012439999999</v>
+      </c>
+      <c r="O73">
+        <v>-0.06357629855999998</v>
+      </c>
+      <c r="P73">
+        <v>-0.20132494544</v>
+      </c>
+      <c r="Q73">
+        <v>-0.3523249454399999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.4589172643431349</v>
+      </c>
+      <c r="T73">
+        <v>1.577842428874573</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.08713607021574574</v>
+      </c>
+      <c r="W73">
+        <v>0.2179919064324799</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3630669592322741</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2898602602265699</v>
+      </c>
+      <c r="C74">
+        <v>-0.1705322956878728</v>
+      </c>
+      <c r="D74">
+        <v>1.551627704312127</v>
+      </c>
+      <c r="E74">
+        <v>0.9431599999999998</v>
+      </c>
+      <c r="F74">
+        <v>1.76616</v>
+      </c>
+      <c r="G74">
+        <v>0.044</v>
+      </c>
+      <c r="H74">
+        <v>1.63</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>-0.151</v>
+      </c>
+      <c r="L74">
+        <v>0.151</v>
+      </c>
+      <c r="M74">
+        <v>0.4217590079999999</v>
+      </c>
+      <c r="N74">
+        <v>-0.270759008</v>
+      </c>
+      <c r="O74">
+        <v>-0.06498216191999999</v>
+      </c>
+      <c r="P74">
+        <v>-0.20577684608</v>
+      </c>
+      <c r="Q74">
+        <v>-0.3567768460799999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.4739214523553897</v>
+      </c>
+      <c r="T74">
+        <v>1.634193944191522</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.08592584701830483</v>
+      </c>
+      <c r="W74">
+        <v>0.2182809077320288</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3580243625762701</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2918602602265699</v>
+      </c>
+      <c r="C75">
+        <v>-0.207325206529132</v>
+      </c>
+      <c r="D75">
+        <v>1.539364793470868</v>
+      </c>
+      <c r="E75">
+        <v>0.9676899999999999</v>
+      </c>
+      <c r="F75">
+        <v>1.79069</v>
+      </c>
+      <c r="G75">
+        <v>0.044</v>
+      </c>
+      <c r="H75">
+        <v>1.63</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>-0.151</v>
+      </c>
+      <c r="L75">
+        <v>0.151</v>
+      </c>
+      <c r="M75">
+        <v>0.427616772</v>
+      </c>
+      <c r="N75">
+        <v>-0.276616772</v>
+      </c>
+      <c r="O75">
+        <v>-0.06638802528</v>
+      </c>
+      <c r="P75">
+        <v>-0.21022874672</v>
+      </c>
+      <c r="Q75">
+        <v>-0.36122874672</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4900370617018857</v>
+      </c>
+      <c r="T75">
+        <v>1.694719645828245</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.0847487806207938</v>
+      </c>
+      <c r="W75">
+        <v>0.2185619911877544</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3531199192533074</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2938602602265699</v>
+      </c>
+      <c r="C76">
+        <v>-0.2439258034312402</v>
+      </c>
+      <c r="D76">
+        <v>1.52729419656876</v>
+      </c>
+      <c r="E76">
+        <v>0.9922199999999999</v>
+      </c>
+      <c r="F76">
+        <v>1.81522</v>
+      </c>
+      <c r="G76">
+        <v>0.044</v>
+      </c>
+      <c r="H76">
+        <v>1.63</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>-0.151</v>
+      </c>
+      <c r="L76">
+        <v>0.151</v>
+      </c>
+      <c r="M76">
+        <v>0.433474536</v>
+      </c>
+      <c r="N76">
+        <v>-0.2824745359999999</v>
+      </c>
+      <c r="O76">
+        <v>-0.06779388863999998</v>
+      </c>
+      <c r="P76">
+        <v>-0.21468064736</v>
+      </c>
+      <c r="Q76">
+        <v>-0.3656806473599999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.5073923333058044</v>
+      </c>
+      <c r="T76">
+        <v>1.759901170667793</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.08360352682862091</v>
+      </c>
+      <c r="W76">
+        <v>0.2188354777933253</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3483480284525872</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2958602602265699</v>
+      </c>
+      <c r="C77">
+        <v>-0.2803385751612824</v>
+      </c>
+      <c r="D77">
+        <v>1.515411424838718</v>
+      </c>
+      <c r="E77">
+        <v>1.01675</v>
+      </c>
+      <c r="F77">
+        <v>1.83975</v>
+      </c>
+      <c r="G77">
+        <v>0.044</v>
+      </c>
+      <c r="H77">
+        <v>1.63</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>-0.151</v>
+      </c>
+      <c r="L77">
+        <v>0.151</v>
+      </c>
+      <c r="M77">
+        <v>0.4393323</v>
+      </c>
+      <c r="N77">
+        <v>-0.2883323</v>
+      </c>
+      <c r="O77">
+        <v>-0.06919975199999999</v>
+      </c>
+      <c r="P77">
+        <v>-0.219132548</v>
+      </c>
+      <c r="Q77">
+        <v>-0.370132548</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.5261360266380365</v>
+      </c>
+      <c r="T77">
+        <v>1.830297217494505</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.08248881313757261</v>
+      </c>
+      <c r="W77">
+        <v>0.2191016714227477</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3437033880732193</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2978602602265699</v>
+      </c>
+      <c r="C78">
+        <v>-0.316567871869418</v>
+      </c>
+      <c r="D78">
+        <v>1.503712128130582</v>
+      </c>
+      <c r="E78">
+        <v>1.04128</v>
+      </c>
+      <c r="F78">
+        <v>1.86428</v>
+      </c>
+      <c r="G78">
+        <v>0.044</v>
+      </c>
+      <c r="H78">
+        <v>1.63</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>-0.151</v>
+      </c>
+      <c r="L78">
+        <v>0.151</v>
+      </c>
+      <c r="M78">
+        <v>0.445190064</v>
+      </c>
+      <c r="N78">
+        <v>-0.294190064</v>
+      </c>
+      <c r="O78">
+        <v>-0.07060561536</v>
+      </c>
+      <c r="P78">
+        <v>-0.22358444864</v>
+      </c>
+      <c r="Q78">
+        <v>-0.3745844486400001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.5464416944146215</v>
+      </c>
+      <c r="T78">
+        <v>1.906559601556776</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.0814034340173414</v>
+      </c>
+      <c r="W78">
+        <v>0.2193608599566589</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3391809750722559</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2998602602265699</v>
+      </c>
+      <c r="C79">
+        <v>-0.3526179103986486</v>
+      </c>
+      <c r="D79">
+        <v>1.492192089601351</v>
+      </c>
+      <c r="E79">
+        <v>1.06581</v>
+      </c>
+      <c r="F79">
+        <v>1.88881</v>
+      </c>
+      <c r="G79">
+        <v>0.044</v>
+      </c>
+      <c r="H79">
+        <v>1.63</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>-0.151</v>
+      </c>
+      <c r="L79">
+        <v>0.151</v>
+      </c>
+      <c r="M79">
+        <v>0.451047828</v>
+      </c>
+      <c r="N79">
+        <v>-0.300047828</v>
+      </c>
+      <c r="O79">
+        <v>-0.07201147871999999</v>
+      </c>
+      <c r="P79">
+        <v>-0.22803634928</v>
+      </c>
+      <c r="Q79">
+        <v>-0.37903634928</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.5685130724326484</v>
+      </c>
+      <c r="T79">
+        <v>1.989453497276636</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.08034624656257074</v>
+      </c>
+      <c r="W79">
+        <v>0.2196133163208581</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3347760273440449</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.3018602602265699</v>
+      </c>
+      <c r="C80">
+        <v>-0.3884927793523723</v>
+      </c>
+      <c r="D80">
+        <v>1.480847220647628</v>
+      </c>
+      <c r="E80">
+        <v>1.09034</v>
+      </c>
+      <c r="F80">
+        <v>1.91334</v>
+      </c>
+      <c r="G80">
+        <v>0.044</v>
+      </c>
+      <c r="H80">
+        <v>1.63</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>-0.151</v>
+      </c>
+      <c r="L80">
+        <v>0.151</v>
+      </c>
+      <c r="M80">
+        <v>0.456905592</v>
+      </c>
+      <c r="N80">
+        <v>-0.305905592</v>
+      </c>
+      <c r="O80">
+        <v>-0.07341734208</v>
+      </c>
+      <c r="P80">
+        <v>-0.23248824992</v>
+      </c>
+      <c r="Q80">
+        <v>-0.38348824992</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.5925909393614053</v>
+      </c>
+      <c r="T80">
+        <v>2.079883201698301</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.07931616647843522</v>
+      </c>
+      <c r="W80">
+        <v>0.2198592994449497</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3304840269934801</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.3038602602265699</v>
+      </c>
+      <c r="C81">
+        <v>-0.4241964439325081</v>
+      </c>
+      <c r="D81">
+        <v>1.469673556067492</v>
+      </c>
+      <c r="E81">
+        <v>1.11487</v>
+      </c>
+      <c r="F81">
+        <v>1.93787</v>
+      </c>
+      <c r="G81">
+        <v>0.044</v>
+      </c>
+      <c r="H81">
+        <v>1.63</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>-0.151</v>
+      </c>
+      <c r="L81">
+        <v>0.151</v>
+      </c>
+      <c r="M81">
+        <v>0.462763356</v>
+      </c>
+      <c r="N81">
+        <v>-0.311763356</v>
+      </c>
+      <c r="O81">
+        <v>-0.07482320544000001</v>
+      </c>
+      <c r="P81">
+        <v>-0.23694015056</v>
+      </c>
+      <c r="Q81">
+        <v>-0.38794015056</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.6189619364738532</v>
+      </c>
+      <c r="T81">
+        <v>2.17892525892203</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.07831216437111324</v>
+      </c>
+      <c r="W81">
+        <v>0.2200990551481782</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3263006848796385</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.3058602602265699</v>
+      </c>
+      <c r="C82">
+        <v>-0.4597327505602378</v>
+      </c>
+      <c r="D82">
+        <v>1.458667249439762</v>
+      </c>
+      <c r="E82">
+        <v>1.1394</v>
+      </c>
+      <c r="F82">
+        <v>1.9624</v>
+      </c>
+      <c r="G82">
+        <v>0.044</v>
+      </c>
+      <c r="H82">
+        <v>1.63</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>-0.151</v>
+      </c>
+      <c r="L82">
+        <v>0.151</v>
+      </c>
+      <c r="M82">
+        <v>0.46862112</v>
+      </c>
+      <c r="N82">
+        <v>-0.31762112</v>
+      </c>
+      <c r="O82">
+        <v>-0.07622906879999999</v>
+      </c>
+      <c r="P82">
+        <v>-0.2413920512</v>
+      </c>
+      <c r="Q82">
+        <v>-0.3923920512</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.6479700332975458</v>
+      </c>
+      <c r="T82">
+        <v>2.287871521868132</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.07733326231647433</v>
+      </c>
+      <c r="W82">
+        <v>0.2203328169588259</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3222219263186431</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3078602602265699</v>
+      </c>
+      <c r="C83">
+        <v>-0.4951054312906544</v>
+      </c>
+      <c r="D83">
+        <v>1.447824568709346</v>
+      </c>
+      <c r="E83">
+        <v>1.16393</v>
+      </c>
+      <c r="F83">
+        <v>1.98693</v>
+      </c>
+      <c r="G83">
+        <v>0.044</v>
+      </c>
+      <c r="H83">
+        <v>1.63</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>-0.151</v>
+      </c>
+      <c r="L83">
+        <v>0.151</v>
+      </c>
+      <c r="M83">
+        <v>0.474478884</v>
+      </c>
+      <c r="N83">
+        <v>-0.323478884</v>
+      </c>
+      <c r="O83">
+        <v>-0.07763493216</v>
+      </c>
+      <c r="P83">
+        <v>-0.24584395184</v>
+      </c>
+      <c r="Q83">
+        <v>-0.39684395184</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.6800316139974165</v>
+      </c>
+      <c r="T83">
+        <v>2.40828581249277</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.07637853068293761</v>
+      </c>
+      <c r="W83">
+        <v>0.2205608068729145</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3182438778455734</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3098602602265699</v>
+      </c>
+      <c r="C84">
+        <v>-0.5303181080319752</v>
+      </c>
+      <c r="D84">
+        <v>1.437141891968025</v>
+      </c>
+      <c r="E84">
+        <v>1.18846</v>
+      </c>
+      <c r="F84">
+        <v>2.01146</v>
+      </c>
+      <c r="G84">
+        <v>0.044</v>
+      </c>
+      <c r="H84">
+        <v>1.63</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>-0.151</v>
+      </c>
+      <c r="L84">
+        <v>0.151</v>
+      </c>
+      <c r="M84">
+        <v>0.480336648</v>
+      </c>
+      <c r="N84">
+        <v>-0.3293366480000001</v>
+      </c>
+      <c r="O84">
+        <v>-0.07904079552000001</v>
+      </c>
+      <c r="P84">
+        <v>-0.2502958524800001</v>
+      </c>
+      <c r="Q84">
+        <v>-0.4012958524800001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.7156555925528287</v>
+      </c>
+      <c r="T84">
+        <v>2.542079468742369</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.07544708518680422</v>
+      </c>
+      <c r="W84">
+        <v>0.2207832360573912</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3143628549450176</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3118602602265699</v>
+      </c>
+      <c r="C85">
+        <v>-0.5653742965793351</v>
+      </c>
+      <c r="D85">
+        <v>1.426615703420665</v>
+      </c>
+      <c r="E85">
+        <v>1.21299</v>
+      </c>
+      <c r="F85">
+        <v>2.03599</v>
+      </c>
+      <c r="G85">
+        <v>0.044</v>
+      </c>
+      <c r="H85">
+        <v>1.63</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>-0.151</v>
+      </c>
+      <c r="L85">
+        <v>0.151</v>
+      </c>
+      <c r="M85">
+        <v>0.486194412</v>
+      </c>
+      <c r="N85">
+        <v>-0.335194412</v>
+      </c>
+      <c r="O85">
+        <v>-0.08044665887999999</v>
+      </c>
+      <c r="P85">
+        <v>-0.25474775312</v>
+      </c>
+      <c r="Q85">
+        <v>-0.40574775312</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.7554706274088776</v>
+      </c>
+      <c r="T85">
+        <v>2.691613555138979</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.07453808416045718</v>
+      </c>
+      <c r="W85">
+        <v>0.2210003055024828</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3105753506685717</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3138602602265699</v>
+      </c>
+      <c r="C86">
+        <v>-0.6002774104726001</v>
+      </c>
+      <c r="D86">
+        <v>1.4162425895274</v>
+      </c>
+      <c r="E86">
+        <v>1.23752</v>
+      </c>
+      <c r="F86">
+        <v>2.06052</v>
+      </c>
+      <c r="G86">
+        <v>0.044</v>
+      </c>
+      <c r="H86">
+        <v>1.63</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>-0.151</v>
+      </c>
+      <c r="L86">
+        <v>0.151</v>
+      </c>
+      <c r="M86">
+        <v>0.492052176</v>
+      </c>
+      <c r="N86">
+        <v>-0.341052176</v>
+      </c>
+      <c r="O86">
+        <v>-0.08185252224</v>
+      </c>
+      <c r="P86">
+        <v>-0.25919965376</v>
+      </c>
+      <c r="Q86">
+        <v>-0.41019965376</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.800262541621932</v>
+      </c>
+      <c r="T86">
+        <v>2.859839402335163</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.07365072601568985</v>
+      </c>
+      <c r="W86">
+        <v>0.2212122066274533</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3068780250653743</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3158602602265699</v>
+      </c>
+      <c r="C87">
+        <v>-0.6350307646870894</v>
+      </c>
+      <c r="D87">
+        <v>1.40601923531291</v>
+      </c>
+      <c r="E87">
+        <v>1.26205</v>
+      </c>
+      <c r="F87">
+        <v>2.08505</v>
+      </c>
+      <c r="G87">
+        <v>0.044</v>
+      </c>
+      <c r="H87">
+        <v>1.63</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>-0.151</v>
+      </c>
+      <c r="L87">
+        <v>0.151</v>
+      </c>
+      <c r="M87">
+        <v>0.49790994</v>
+      </c>
+      <c r="N87">
+        <v>-0.34690994</v>
+      </c>
+      <c r="O87">
+        <v>-0.08325838559999998</v>
+      </c>
+      <c r="P87">
+        <v>-0.2636515544</v>
+      </c>
+      <c r="Q87">
+        <v>-0.4146515544</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.8510267110633942</v>
+      </c>
+      <c r="T87">
+        <v>3.050495362490842</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.07278424688609349</v>
+      </c>
+      <c r="W87">
+        <v>0.2214191218436009</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.303267695358723</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3178602602265699</v>
+      </c>
+      <c r="C88">
+        <v>-0.6696375791655922</v>
+      </c>
+      <c r="D88">
+        <v>1.395942420834408</v>
+      </c>
+      <c r="E88">
+        <v>1.28658</v>
+      </c>
+      <c r="F88">
+        <v>2.10958</v>
+      </c>
+      <c r="G88">
+        <v>0.044</v>
+      </c>
+      <c r="H88">
+        <v>1.63</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>-0.151</v>
+      </c>
+      <c r="L88">
+        <v>0.151</v>
+      </c>
+      <c r="M88">
+        <v>0.5037677039999999</v>
+      </c>
+      <c r="N88">
+        <v>-0.3527677039999999</v>
+      </c>
+      <c r="O88">
+        <v>-0.08466424895999998</v>
+      </c>
+      <c r="P88">
+        <v>-0.2681034550399999</v>
+      </c>
+      <c r="Q88">
+        <v>-0.4191034550399999</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.9090429047107795</v>
+      </c>
+      <c r="T88">
+        <v>3.268387888383045</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.07193791843392962</v>
+      </c>
+      <c r="W88">
+        <v>0.2216212250779776</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2997413268080402</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3198602602265699</v>
+      </c>
+      <c r="C89">
+        <v>-0.7041009821995827</v>
+      </c>
+      <c r="D89">
+        <v>1.386009017800417</v>
+      </c>
+      <c r="E89">
+        <v>1.31111</v>
+      </c>
+      <c r="F89">
+        <v>2.13411</v>
+      </c>
+      <c r="G89">
+        <v>0.044</v>
+      </c>
+      <c r="H89">
+        <v>1.63</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>-0.151</v>
+      </c>
+      <c r="L89">
+        <v>0.151</v>
+      </c>
+      <c r="M89">
+        <v>0.509625468</v>
+      </c>
+      <c r="N89">
+        <v>-0.3586254679999999</v>
+      </c>
+      <c r="O89">
+        <v>-0.08607011231999999</v>
+      </c>
+      <c r="P89">
+        <v>-0.2725553556799999</v>
+      </c>
+      <c r="Q89">
+        <v>-0.4235553556799999</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.9759846666116088</v>
+      </c>
+      <c r="T89">
+        <v>3.519802341335587</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.07111104580825227</v>
+      </c>
+      <c r="W89">
+        <v>0.2218186822609894</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2962960242010512</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3218602602265699</v>
+      </c>
+      <c r="C90">
+        <v>-0.7384240136670941</v>
+      </c>
+      <c r="D90">
+        <v>1.376215986332906</v>
+      </c>
+      <c r="E90">
+        <v>1.33564</v>
+      </c>
+      <c r="F90">
+        <v>2.15864</v>
+      </c>
+      <c r="G90">
+        <v>0.044</v>
+      </c>
+      <c r="H90">
+        <v>1.63</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>-0.151</v>
+      </c>
+      <c r="L90">
+        <v>0.151</v>
+      </c>
+      <c r="M90">
+        <v>0.5154832319999999</v>
+      </c>
+      <c r="N90">
+        <v>-0.3644832319999999</v>
+      </c>
+      <c r="O90">
+        <v>-0.08747597567999997</v>
+      </c>
+      <c r="P90">
+        <v>-0.2770072563199999</v>
+      </c>
+      <c r="Q90">
+        <v>-0.4280072563199999</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.054083388829243</v>
+      </c>
+      <c r="T90">
+        <v>3.813119203113553</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.07030296574224941</v>
+      </c>
+      <c r="W90">
+        <v>0.2220116517807509</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2929290239260393</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3238602602265699</v>
+      </c>
+      <c r="C91">
+        <v>-0.7726096281342889</v>
+      </c>
+      <c r="D91">
+        <v>1.366560371865711</v>
+      </c>
+      <c r="E91">
+        <v>1.36017</v>
+      </c>
+      <c r="F91">
+        <v>2.18317</v>
+      </c>
+      <c r="G91">
+        <v>0.044</v>
+      </c>
+      <c r="H91">
+        <v>1.63</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>-0.151</v>
+      </c>
+      <c r="L91">
+        <v>0.151</v>
+      </c>
+      <c r="M91">
+        <v>0.5213409960000001</v>
+      </c>
+      <c r="N91">
+        <v>-0.370340996</v>
+      </c>
+      <c r="O91">
+        <v>-0.08888183904000001</v>
+      </c>
+      <c r="P91">
+        <v>-0.28145915696</v>
+      </c>
+      <c r="Q91">
+        <v>-0.43245915696</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.14638187872281</v>
+      </c>
+      <c r="T91">
+        <v>4.159766403396603</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.06951304477885333</v>
+      </c>
+      <c r="W91">
+        <v>0.2222002849068098</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2896376865785556</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3258602602265699</v>
+      </c>
+      <c r="C92">
+        <v>-0.8066606978273709</v>
+      </c>
+      <c r="D92">
+        <v>1.357039302172629</v>
+      </c>
+      <c r="E92">
+        <v>1.3847</v>
+      </c>
+      <c r="F92">
+        <v>2.2077</v>
+      </c>
+      <c r="G92">
+        <v>0.044</v>
+      </c>
+      <c r="H92">
+        <v>1.63</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>-0.151</v>
+      </c>
+      <c r="L92">
+        <v>0.151</v>
+      </c>
+      <c r="M92">
+        <v>0.52719876</v>
+      </c>
+      <c r="N92">
+        <v>-0.37619876</v>
+      </c>
+      <c r="O92">
+        <v>-0.09028770239999999</v>
+      </c>
+      <c r="P92">
+        <v>-0.2859110576</v>
+      </c>
+      <c r="Q92">
+        <v>-0.4369110575999999</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.257140066595092</v>
+      </c>
+      <c r="T92">
+        <v>4.575743043736264</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.06874067761464385</v>
+      </c>
+      <c r="W92">
+        <v>0.222384726185623</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2864194900610161</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3278602602265699</v>
+      </c>
+      <c r="C93">
+        <v>-0.8405800154811289</v>
+      </c>
+      <c r="D93">
+        <v>1.347649984518871</v>
+      </c>
+      <c r="E93">
+        <v>1.40923</v>
+      </c>
+      <c r="F93">
+        <v>2.23223</v>
+      </c>
+      <c r="G93">
+        <v>0.044</v>
+      </c>
+      <c r="H93">
+        <v>1.63</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>-0.151</v>
+      </c>
+      <c r="L93">
+        <v>0.151</v>
+      </c>
+      <c r="M93">
+        <v>0.533056524</v>
+      </c>
+      <c r="N93">
+        <v>-0.382056524</v>
+      </c>
+      <c r="O93">
+        <v>-0.09169356576</v>
+      </c>
+      <c r="P93">
+        <v>-0.29036295824</v>
+      </c>
+      <c r="Q93">
+        <v>-0.44136295824</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.392511185105657</v>
+      </c>
+      <c r="T93">
+        <v>5.084158937484737</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.06798528555294446</v>
+      </c>
+      <c r="W93">
+        <v>0.2225651138099569</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2832720231372686</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3298602602265699</v>
+      </c>
+      <c r="C94">
+        <v>-0.8743702970700329</v>
+      </c>
+      <c r="D94">
+        <v>1.338389702929967</v>
+      </c>
+      <c r="E94">
+        <v>1.43376</v>
+      </c>
+      <c r="F94">
+        <v>2.25676</v>
+      </c>
+      <c r="G94">
+        <v>0.044</v>
+      </c>
+      <c r="H94">
+        <v>1.63</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>-0.151</v>
+      </c>
+      <c r="L94">
+        <v>0.151</v>
+      </c>
+      <c r="M94">
+        <v>0.538914288</v>
+      </c>
+      <c r="N94">
+        <v>-0.3879142879999999</v>
+      </c>
+      <c r="O94">
+        <v>-0.09309942911999998</v>
+      </c>
+      <c r="P94">
+        <v>-0.29481485888</v>
+      </c>
+      <c r="Q94">
+        <v>-0.4458148588799999</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.561725083243865</v>
+      </c>
+      <c r="T94">
+        <v>5.719678804670331</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.06724631505780378</v>
+      </c>
+      <c r="W94">
+        <v>0.2227415799641965</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2801929794075158</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3318602602265699</v>
+      </c>
+      <c r="C95">
+        <v>-0.9080341844275013</v>
+      </c>
+      <c r="D95">
+        <v>1.329255815572499</v>
+      </c>
+      <c r="E95">
+        <v>1.45829</v>
+      </c>
+      <c r="F95">
+        <v>2.28129</v>
+      </c>
+      <c r="G95">
+        <v>0.044</v>
+      </c>
+      <c r="H95">
+        <v>1.63</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>-0.151</v>
+      </c>
+      <c r="L95">
+        <v>0.151</v>
+      </c>
+      <c r="M95">
+        <v>0.544772052</v>
+      </c>
+      <c r="N95">
+        <v>-0.393772052</v>
+      </c>
+      <c r="O95">
+        <v>-0.09450529247999999</v>
+      </c>
+      <c r="P95">
+        <v>-0.29926675952</v>
+      </c>
+      <c r="Q95">
+        <v>-0.4502667595199999</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.77928580942156</v>
+      </c>
+      <c r="T95">
+        <v>6.536775776766094</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.06652323640126824</v>
+      </c>
+      <c r="W95">
+        <v>0.2229142511473771</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2771801516719511</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3338602602265699</v>
+      </c>
+      <c r="C96">
+        <v>-0.9415742477586448</v>
+      </c>
+      <c r="D96">
+        <v>1.320245752241355</v>
+      </c>
+      <c r="E96">
+        <v>1.48282</v>
+      </c>
+      <c r="F96">
+        <v>2.30582</v>
+      </c>
+      <c r="G96">
+        <v>0.044</v>
+      </c>
+      <c r="H96">
+        <v>1.63</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>-0.151</v>
+      </c>
+      <c r="L96">
+        <v>0.151</v>
+      </c>
+      <c r="M96">
+        <v>0.550629816</v>
+      </c>
+      <c r="N96">
+        <v>-0.399629816</v>
+      </c>
+      <c r="O96">
+        <v>-0.09591115584</v>
+      </c>
+      <c r="P96">
+        <v>-0.30371866016</v>
+      </c>
+      <c r="Q96">
+        <v>-0.4547186601600001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.069366777658487</v>
+      </c>
+      <c r="T96">
+        <v>7.626238406227111</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.06581554239699942</v>
+      </c>
+      <c r="W96">
+        <v>0.2230832484755965</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2742314266541643</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3358602602265699</v>
+      </c>
+      <c r="C97">
+        <v>-0.9749929880515027</v>
+      </c>
+      <c r="D97">
+        <v>1.311357011948497</v>
+      </c>
+      <c r="E97">
+        <v>1.50735</v>
+      </c>
+      <c r="F97">
+        <v>2.33035</v>
+      </c>
+      <c r="G97">
+        <v>0.044</v>
+      </c>
+      <c r="H97">
+        <v>1.63</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>-0.151</v>
+      </c>
+      <c r="L97">
+        <v>0.151</v>
+      </c>
+      <c r="M97">
+        <v>0.5564875800000001</v>
+      </c>
+      <c r="N97">
+        <v>-0.4054875800000001</v>
+      </c>
+      <c r="O97">
+        <v>-0.09731701920000001</v>
+      </c>
+      <c r="P97">
+        <v>-0.3081705608</v>
+      </c>
+      <c r="Q97">
+        <v>-0.4591705608000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.475480133190186</v>
+      </c>
+      <c r="T97">
+        <v>9.151486087472538</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.06512274721387312</v>
+      </c>
+      <c r="W97">
+        <v>0.2232486879653271</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2713447800578047</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3378602602265699</v>
+      </c>
+      <c r="C98">
+        <v>-1.00829283939153</v>
+      </c>
+      <c r="D98">
+        <v>1.30258716060847</v>
+      </c>
+      <c r="E98">
+        <v>1.53188</v>
+      </c>
+      <c r="F98">
+        <v>2.35488</v>
+      </c>
+      <c r="G98">
+        <v>0.044</v>
+      </c>
+      <c r="H98">
+        <v>1.63</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>-0.151</v>
+      </c>
+      <c r="L98">
+        <v>0.151</v>
+      </c>
+      <c r="M98">
+        <v>0.5623453439999999</v>
+      </c>
+      <c r="N98">
+        <v>-0.4113453439999999</v>
+      </c>
+      <c r="O98">
+        <v>-0.09872288255999997</v>
+      </c>
+      <c r="P98">
+        <v>-0.3126224614399999</v>
+      </c>
+      <c r="Q98">
+        <v>-0.46362246144</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>3.084650166487726</v>
+      </c>
+      <c r="T98">
+        <v>11.43935760934065</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.06444438526372863</v>
+      </c>
+      <c r="W98">
+        <v>0.2234106807990216</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2685182719322027</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3398602602265699</v>
+      </c>
+      <c r="C99">
+        <v>-1.041476171183831</v>
+      </c>
+      <c r="D99">
+        <v>1.293933828816169</v>
+      </c>
+      <c r="E99">
+        <v>1.55641</v>
+      </c>
+      <c r="F99">
+        <v>2.37941</v>
+      </c>
+      <c r="G99">
+        <v>0.044</v>
+      </c>
+      <c r="H99">
+        <v>1.63</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>-0.151</v>
+      </c>
+      <c r="L99">
+        <v>0.151</v>
+      </c>
+      <c r="M99">
+        <v>0.568203108</v>
+      </c>
+      <c r="N99">
+        <v>-0.4172031079999999</v>
+      </c>
+      <c r="O99">
+        <v>-0.10012874592</v>
+      </c>
+      <c r="P99">
+        <v>-0.3170743620799999</v>
+      </c>
+      <c r="Q99">
+        <v>-0.46807436208</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>4.099933555316968</v>
+      </c>
+      <c r="T99">
+        <v>15.2524768124542</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.06378001015791698</v>
+      </c>
+      <c r="W99">
+        <v>0.2235693335742894</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2657500423246542</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3418602602265699</v>
+      </c>
+      <c r="C100">
+        <v>-1.074545290287397</v>
+      </c>
+      <c r="D100">
+        <v>1.285394709712603</v>
+      </c>
+      <c r="E100">
+        <v>1.58094</v>
+      </c>
+      <c r="F100">
+        <v>2.40394</v>
+      </c>
+      <c r="G100">
+        <v>0.044</v>
+      </c>
+      <c r="H100">
+        <v>1.63</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>-0.151</v>
+      </c>
+      <c r="L100">
+        <v>0.151</v>
+      </c>
+      <c r="M100">
+        <v>0.574060872</v>
+      </c>
+      <c r="N100">
+        <v>-0.423060872</v>
+      </c>
+      <c r="O100">
+        <v>-0.10153460928</v>
+      </c>
+      <c r="P100">
+        <v>-0.32152626272</v>
+      </c>
+      <c r="Q100">
+        <v>-0.47252626272</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>6.130500332975451</v>
+      </c>
+      <c r="T100">
+        <v>22.87871521868129</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.06312919372773415</v>
+      </c>
+      <c r="W100">
+        <v>0.2237247485378171</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2630383071988923</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3438602602265699</v>
+      </c>
+      <c r="C101">
+        <v>-1.107502443065395</v>
+      </c>
+      <c r="D101">
+        <v>1.276967556934605</v>
+      </c>
+      <c r="E101">
+        <v>1.60547</v>
+      </c>
+      <c r="F101">
+        <v>2.42847</v>
+      </c>
+      <c r="G101">
+        <v>0.044</v>
+      </c>
+      <c r="H101">
+        <v>1.63</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>-0.151</v>
+      </c>
+      <c r="L101">
+        <v>0.151</v>
+      </c>
+      <c r="M101">
+        <v>0.579918636</v>
+      </c>
+      <c r="N101">
+        <v>-0.428918636</v>
+      </c>
+      <c r="O101">
+        <v>-0.10294047264</v>
+      </c>
+      <c r="P101">
+        <v>-0.32597816336</v>
+      </c>
+      <c r="Q101">
+        <v>-0.47697816336</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>12.22220066595091</v>
+      </c>
+      <c r="T101">
+        <v>45.75743043736259</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.06249152510422167</v>
+      </c>
+      <c r="W101">
+        <v>0.2238770238051119</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2603813546009237</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
